--- a/Municipios_Colombia_geocodificado.xlsx
+++ b/Municipios_Colombia_geocodificado.xlsx
@@ -11249,8 +11249,12 @@
           <t>San Bernardo</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
+      <c r="C602" t="n">
+        <v>4.178282</v>
+      </c>
+      <c r="D602" t="n">
+        <v>-74.422273</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -11263,8 +11267,12 @@
           <t>San Cayetano</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
+      <c r="C603" t="n">
+        <v>5.333051</v>
+      </c>
+      <c r="D603" t="n">
+        <v>-74.066783</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -11277,8 +11285,12 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
+      <c r="C604" t="n">
+        <v>4.953252</v>
+      </c>
+      <c r="D604" t="n">
+        <v>-74.264573</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -11291,8 +11303,12 @@
           <t>San Juan de Rioseco</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr"/>
-      <c r="D605" t="inlineStr"/>
+      <c r="C605" t="n">
+        <v>4.845516</v>
+      </c>
+      <c r="D605" t="n">
+        <v>-74.62253699999999</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -11305,8 +11321,12 @@
           <t>Sasaima</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
+      <c r="C606" t="n">
+        <v>4.964577</v>
+      </c>
+      <c r="D606" t="n">
+        <v>-74.433115</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -11319,8 +11339,12 @@
           <t>Sesquilé</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
-      <c r="D607" t="inlineStr"/>
+      <c r="C607" t="n">
+        <v>5.044767</v>
+      </c>
+      <c r="D607" t="n">
+        <v>-73.795553</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -11333,8 +11357,12 @@
           <t>Sibaté</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr"/>
-      <c r="D608" t="inlineStr"/>
+      <c r="C608" t="n">
+        <v>4.466006</v>
+      </c>
+      <c r="D608" t="n">
+        <v>-74.26272400000001</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -11347,8 +11375,12 @@
           <t>Silvania</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
-      <c r="D609" t="inlineStr"/>
+      <c r="C609" t="n">
+        <v>4.404854</v>
+      </c>
+      <c r="D609" t="n">
+        <v>-74.387241</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -11361,8 +11393,12 @@
           <t>Simijaca</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
-      <c r="D610" t="inlineStr"/>
+      <c r="C610" t="n">
+        <v>5.515275</v>
+      </c>
+      <c r="D610" t="n">
+        <v>-73.837687</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -11375,8 +11411,12 @@
           <t>Soacha</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr"/>
-      <c r="D611" t="inlineStr"/>
+      <c r="C611" t="n">
+        <v>4.577959</v>
+      </c>
+      <c r="D611" t="n">
+        <v>-74.22386400000001</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -11389,8 +11429,12 @@
           <t>Sopó</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr"/>
-      <c r="D612" t="inlineStr"/>
+      <c r="C612" t="n">
+        <v>4.907916</v>
+      </c>
+      <c r="D612" t="n">
+        <v>-73.94023300000001</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -11403,8 +11447,12 @@
           <t>Subachoque</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr"/>
-      <c r="D613" t="inlineStr"/>
+      <c r="C613" t="n">
+        <v>4.965903</v>
+      </c>
+      <c r="D613" t="n">
+        <v>-74.166858</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -11417,8 +11465,12 @@
           <t>Suesca</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr"/>
-      <c r="D614" t="inlineStr"/>
+      <c r="C614" t="n">
+        <v>5.103341</v>
+      </c>
+      <c r="D614" t="n">
+        <v>-73.79900600000001</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -11431,8 +11483,12 @@
           <t>Supatá</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr"/>
-      <c r="D615" t="inlineStr"/>
+      <c r="C615" t="n">
+        <v>5.057235</v>
+      </c>
+      <c r="D615" t="n">
+        <v>-74.232271</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -11445,8 +11501,12 @@
           <t>Susa</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr"/>
-      <c r="D616" t="inlineStr"/>
+      <c r="C616" t="n">
+        <v>5.438794</v>
+      </c>
+      <c r="D616" t="n">
+        <v>-73.839607</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -11459,8 +11519,12 @@
           <t>Sutatausa</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr"/>
+      <c r="C617" t="n">
+        <v>5.237734</v>
+      </c>
+      <c r="D617" t="n">
+        <v>-73.85494</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -11473,8 +11537,12 @@
           <t>Tabio</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr"/>
-      <c r="D618" t="inlineStr"/>
+      <c r="C618" t="n">
+        <v>4.914012</v>
+      </c>
+      <c r="D618" t="n">
+        <v>-74.098883</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -11487,8 +11555,12 @@
           <t>Tausa</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr"/>
+      <c r="C619" t="n">
+        <v>5.194927</v>
+      </c>
+      <c r="D619" t="n">
+        <v>-73.95630800000001</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -11501,8 +11573,12 @@
           <t>Tena</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr"/>
+      <c r="C620" t="n">
+        <v>4.64658</v>
+      </c>
+      <c r="D620" t="n">
+        <v>-74.40078</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -11515,8 +11591,12 @@
           <t>Tenjo</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr"/>
-      <c r="D621" t="inlineStr"/>
+      <c r="C621" t="n">
+        <v>4.827454</v>
+      </c>
+      <c r="D621" t="n">
+        <v>-74.152985</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -11529,8 +11609,12 @@
           <t>Tibacuy</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr"/>
-      <c r="D622" t="inlineStr"/>
+      <c r="C622" t="n">
+        <v>4.347676</v>
+      </c>
+      <c r="D622" t="n">
+        <v>-74.45273</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -11543,8 +11627,12 @@
           <t>Tibirita</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr"/>
-      <c r="D623" t="inlineStr"/>
+      <c r="C623" t="n">
+        <v>5.083543</v>
+      </c>
+      <c r="D623" t="n">
+        <v>-73.51651</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -11557,8 +11645,12 @@
           <t>Tocaima</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr"/>
+      <c r="C624" t="n">
+        <v>4.457927</v>
+      </c>
+      <c r="D624" t="n">
+        <v>-74.63422300000001</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -11571,8 +11663,12 @@
           <t>Tocancipá</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr"/>
-      <c r="D625" t="inlineStr"/>
+      <c r="C625" t="n">
+        <v>4.97371</v>
+      </c>
+      <c r="D625" t="n">
+        <v>-73.92118000000001</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -11585,8 +11681,12 @@
           <t>Topaipí</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr"/>
-      <c r="D626" t="inlineStr"/>
+      <c r="C626" t="n">
+        <v>5.3353896</v>
+      </c>
+      <c r="D626" t="n">
+        <v>-74.30268119999999</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -11599,8 +11699,12 @@
           <t>Ubalá</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr"/>
-      <c r="D627" t="inlineStr"/>
+      <c r="C627" t="n">
+        <v>4.745638</v>
+      </c>
+      <c r="D627" t="n">
+        <v>-73.532979</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -11613,8 +11717,12 @@
           <t>Ubaque</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr"/>
-      <c r="D628" t="inlineStr"/>
+      <c r="C628" t="n">
+        <v>4.501443</v>
+      </c>
+      <c r="D628" t="n">
+        <v>-73.97103</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -11627,8 +11735,12 @@
           <t>Ubaté</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr"/>
-      <c r="D629" t="inlineStr"/>
+      <c r="C629" t="n">
+        <v>5.309063</v>
+      </c>
+      <c r="D629" t="n">
+        <v>-73.81760199999999</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -11641,8 +11753,12 @@
           <t>Une</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
+      <c r="C630" t="n">
+        <v>4.298226</v>
+      </c>
+      <c r="D630" t="n">
+        <v>-74.07789200000001</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -11655,8 +11771,12 @@
           <t>Útica</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
+      <c r="C631" t="n">
+        <v>5.18792</v>
+      </c>
+      <c r="D631" t="n">
+        <v>-74.481477</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -11669,8 +11789,12 @@
           <t>Venecia</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr"/>
-      <c r="D632" t="inlineStr"/>
+      <c r="C632" t="n">
+        <v>4.088946</v>
+      </c>
+      <c r="D632" t="n">
+        <v>-74.47844600000001</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -11683,8 +11807,12 @@
           <t>Vergara</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="C633" t="n">
+        <v>5.118376</v>
+      </c>
+      <c r="D633" t="n">
+        <v>-74.345186</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -11697,8 +11825,12 @@
           <t>Vianí</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
+      <c r="C634" t="n">
+        <v>4.87426</v>
+      </c>
+      <c r="D634" t="n">
+        <v>-74.562405</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -11711,8 +11843,12 @@
           <t>Villagómez</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
+      <c r="C635" t="n">
+        <v>5.273168</v>
+      </c>
+      <c r="D635" t="n">
+        <v>-74.195178</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -11725,8 +11861,12 @@
           <t>Villapinzón</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
+      <c r="C636" t="n">
+        <v>5.221521</v>
+      </c>
+      <c r="D636" t="n">
+        <v>-73.58989</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -11739,8 +11879,12 @@
           <t>Villeta</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
-      <c r="D637" t="inlineStr"/>
+      <c r="C637" t="n">
+        <v>5.011258</v>
+      </c>
+      <c r="D637" t="n">
+        <v>-74.47023</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -11753,8 +11897,12 @@
           <t>Viotá</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
+      <c r="C638" t="n">
+        <v>4.438888</v>
+      </c>
+      <c r="D638" t="n">
+        <v>-74.523358</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -11767,8 +11915,12 @@
           <t>Yacopí</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
+      <c r="C639" t="n">
+        <v>5.458791</v>
+      </c>
+      <c r="D639" t="n">
+        <v>-74.33761</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -11781,8 +11933,12 @@
           <t>Zipacón</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
+      <c r="C640" t="n">
+        <v>4.752766</v>
+      </c>
+      <c r="D640" t="n">
+        <v>-74.379569</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -11795,8 +11951,12 @@
           <t>Zipaquirá</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
+      <c r="C641" t="n">
+        <v>5.023475</v>
+      </c>
+      <c r="D641" t="n">
+        <v>-74.00398199999999</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -11809,8 +11969,12 @@
           <t>Barrancominas</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr"/>
+      <c r="C642" t="n">
+        <v>3.494239</v>
+      </c>
+      <c r="D642" t="n">
+        <v>-69.813261</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -11823,8 +11987,12 @@
           <t>Cacahual</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
+      <c r="C643" t="n">
+        <v>3.445251</v>
+      </c>
+      <c r="D643" t="n">
+        <v>-67.55558499999999</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -11837,8 +12005,12 @@
           <t>La Guadalupe</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
+      <c r="C644" t="n">
+        <v>1.429011</v>
+      </c>
+      <c r="D644" t="n">
+        <v>-66.998486</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -11851,8 +12023,12 @@
           <t>Mapiripana</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
+      <c r="C645" t="n">
+        <v>2.776245</v>
+      </c>
+      <c r="D645" t="n">
+        <v>-70.447335</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -11865,8 +12041,12 @@
           <t>Morichal Nuevo</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
+      <c r="C646" t="n">
+        <v>2.264983</v>
+      </c>
+      <c r="D646" t="n">
+        <v>-69.918938</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -11879,8 +12059,12 @@
           <t>Pana Pana</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
+      <c r="C647" t="n">
+        <v>2.063372</v>
+      </c>
+      <c r="D647" t="n">
+        <v>-69.084847</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -11893,8 +12077,12 @@
           <t>Puerto Colombia</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
+      <c r="C648" t="n">
+        <v>2.495496</v>
+      </c>
+      <c r="D648" t="n">
+        <v>-68.270511</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -11907,8 +12095,12 @@
           <t>San Felipe</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
+      <c r="C649" t="n">
+        <v>1.913029</v>
+      </c>
+      <c r="D649" t="n">
+        <v>-67.068313</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -11921,8 +12113,12 @@
           <t>Ínirida</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
-      <c r="D650" t="inlineStr"/>
+      <c r="C650" t="n">
+        <v>3.865037</v>
+      </c>
+      <c r="D650" t="n">
+        <v>-67.925985</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -11935,8 +12131,12 @@
           <t>Calamar</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr"/>
+      <c r="C651" t="n">
+        <v>1.5496</v>
+      </c>
+      <c r="D651" t="n">
+        <v>-72.97119000000001</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -11949,8 +12149,12 @@
           <t>El Retorno</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr"/>
-      <c r="D652" t="inlineStr"/>
+      <c r="C652" t="n">
+        <v>2.330502</v>
+      </c>
+      <c r="D652" t="n">
+        <v>-72.626418</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -11963,8 +12167,12 @@
           <t>Miraflores</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
+      <c r="C653" t="n">
+        <v>1.326699</v>
+      </c>
+      <c r="D653" t="n">
+        <v>-72.08680699999999</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -11977,8 +12185,12 @@
           <t>San José del Guaviare</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
+      <c r="C654" t="n">
+        <v>2.571614</v>
+      </c>
+      <c r="D654" t="n">
+        <v>-72.642651</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -11991,8 +12203,12 @@
           <t>Acevedo</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
+      <c r="C655" t="n">
+        <v>1.807045</v>
+      </c>
+      <c r="D655" t="n">
+        <v>-75.88850100000001</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12005,8 +12221,12 @@
           <t>Agrado</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr"/>
-      <c r="D656" t="inlineStr"/>
+      <c r="C656" t="n">
+        <v>2.263296</v>
+      </c>
+      <c r="D656" t="n">
+        <v>-75.71500399999999</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -12019,8 +12239,12 @@
           <t>Aipe</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
+      <c r="C657" t="n">
+        <v>3.222356</v>
+      </c>
+      <c r="D657" t="n">
+        <v>-75.23996200000001</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -12033,8 +12257,12 @@
           <t>Algeciras</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr"/>
-      <c r="D658" t="inlineStr"/>
+      <c r="C658" t="n">
+        <v>2.504681</v>
+      </c>
+      <c r="D658" t="n">
+        <v>-75.30394800000001</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -12047,8 +12275,12 @@
           <t>Altamira</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr"/>
-      <c r="D659" t="inlineStr"/>
+      <c r="C659" t="n">
+        <v>2.082326</v>
+      </c>
+      <c r="D659" t="n">
+        <v>-75.775479</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -12061,8 +12293,12 @@
           <t>Baraya</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
+      <c r="C660" t="n">
+        <v>3.089274</v>
+      </c>
+      <c r="D660" t="n">
+        <v>-74.944835</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -12075,8 +12311,12 @@
           <t>Campoalegre</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr"/>
+      <c r="C661" t="n">
+        <v>2.689539</v>
+      </c>
+      <c r="D661" t="n">
+        <v>-75.323392</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -12089,8 +12329,12 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
+      <c r="C662" t="n">
+        <v>3.375899</v>
+      </c>
+      <c r="D662" t="n">
+        <v>-74.80193</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -12103,8 +12347,12 @@
           <t>Elías</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr"/>
-      <c r="D663" t="inlineStr"/>
+      <c r="C663" t="n">
+        <v>2.013619</v>
+      </c>
+      <c r="D663" t="n">
+        <v>-75.939234</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -12117,8 +12365,12 @@
           <t>Neiva</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr"/>
+      <c r="C664" t="n">
+        <v>2.925704</v>
+      </c>
+      <c r="D664" t="n">
+        <v>-75.289394</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -12131,8 +12383,12 @@
           <t>Garzón</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
+      <c r="C665" t="n">
+        <v>2.196013</v>
+      </c>
+      <c r="D665" t="n">
+        <v>-75.627484</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -12145,8 +12401,12 @@
           <t>Gigante</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
+      <c r="C666" t="n">
+        <v>2.394845</v>
+      </c>
+      <c r="D666" t="n">
+        <v>-75.52692399999999</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -12159,8 +12419,12 @@
           <t>Guadalupe</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
+      <c r="C667" t="n">
+        <v>2.024878</v>
+      </c>
+      <c r="D667" t="n">
+        <v>-75.756405</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -12173,8 +12437,12 @@
           <t>Hobo</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr"/>
+      <c r="C668" t="n">
+        <v>2.581104</v>
+      </c>
+      <c r="D668" t="n">
+        <v>-75.4495</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -12187,8 +12455,12 @@
           <t>Íquira</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr"/>
+      <c r="C669" t="n">
+        <v>2.649928</v>
+      </c>
+      <c r="D669" t="n">
+        <v>-75.63520800000001</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -12201,8 +12473,12 @@
           <t>Isnos</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr"/>
-      <c r="D670" t="inlineStr"/>
+      <c r="C670" t="n">
+        <v>1.929072</v>
+      </c>
+      <c r="D670" t="n">
+        <v>-76.216052</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -12215,8 +12491,12 @@
           <t>La Argentina</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr"/>
-      <c r="D671" t="inlineStr"/>
+      <c r="C671" t="n">
+        <v>2.198572</v>
+      </c>
+      <c r="D671" t="n">
+        <v>-75.97911499999999</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -12229,8 +12509,12 @@
           <t>La Plata</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
+      <c r="C672" t="n">
+        <v>2.389415</v>
+      </c>
+      <c r="D672" t="n">
+        <v>-75.892624</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -12243,8 +12527,12 @@
           <t>Nátaga</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
+      <c r="C673" t="n">
+        <v>2.576959</v>
+      </c>
+      <c r="D673" t="n">
+        <v>-75.79512</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -12257,8 +12545,12 @@
           <t>Oporapa</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
+      <c r="C674" t="n">
+        <v>2.023576</v>
+      </c>
+      <c r="D674" t="n">
+        <v>-75.995126</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -12271,8 +12563,12 @@
           <t>Paicol</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
+      <c r="C675" t="n">
+        <v>2.448713</v>
+      </c>
+      <c r="D675" t="n">
+        <v>-75.774749</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -12285,8 +12581,12 @@
           <t>Palermo</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
+      <c r="C676" t="n">
+        <v>2.889696</v>
+      </c>
+      <c r="D676" t="n">
+        <v>-75.434659</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -12299,8 +12599,12 @@
           <t>Palestina</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
+      <c r="C677" t="n">
+        <v>1.722951</v>
+      </c>
+      <c r="D677" t="n">
+        <v>-76.13118799999999</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -12313,8 +12617,12 @@
           <t>Pital</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr"/>
-      <c r="D678" t="inlineStr"/>
+      <c r="C678" t="n">
+        <v>2.257469</v>
+      </c>
+      <c r="D678" t="n">
+        <v>-75.83396999999999</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -12327,8 +12635,12 @@
           <t>Pitalito</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
+      <c r="C679" t="n">
+        <v>1.8447122</v>
+      </c>
+      <c r="D679" t="n">
+        <v>-76.04568860000001</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -12341,8 +12653,12 @@
           <t>Rivera</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
+      <c r="C680" t="n">
+        <v>2.77764</v>
+      </c>
+      <c r="D680" t="n">
+        <v>-75.25721799999999</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -12355,8 +12671,12 @@
           <t>Saladoblando</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
+      <c r="C681" t="n">
+        <v>1.993142</v>
+      </c>
+      <c r="D681" t="n">
+        <v>-76.045035</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -12369,8 +12689,12 @@
           <t>San Agustín</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr"/>
+      <c r="C682" t="n">
+        <v>1.882076</v>
+      </c>
+      <c r="D682" t="n">
+        <v>-76.272898</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -12383,8 +12707,12 @@
           <t>Santa María</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
+      <c r="C683" t="n">
+        <v>2.937493</v>
+      </c>
+      <c r="D683" t="n">
+        <v>-75.58674999999999</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -12397,8 +12725,12 @@
           <t>Suaza</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
+      <c r="C684" t="n">
+        <v>1.977287</v>
+      </c>
+      <c r="D684" t="n">
+        <v>-75.79462700000001</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -12411,8 +12743,12 @@
           <t>Tarqui</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
+      <c r="C685" t="n">
+        <v>2.113689</v>
+      </c>
+      <c r="D685" t="n">
+        <v>-75.825174</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -12425,8 +12761,12 @@
           <t>Tello</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr"/>
+      <c r="C686" t="n">
+        <v>3.067211</v>
+      </c>
+      <c r="D686" t="n">
+        <v>-75.139285</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -12439,8 +12779,12 @@
           <t>Teruel</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
+      <c r="C687" t="n">
+        <v>2.741633</v>
+      </c>
+      <c r="D687" t="n">
+        <v>-75.56834499999999</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -12453,8 +12797,12 @@
           <t>Tesalia</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
+      <c r="C688" t="n">
+        <v>2.485581</v>
+      </c>
+      <c r="D688" t="n">
+        <v>-75.72732999999999</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -12467,8 +12815,12 @@
           <t>Timaná</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr"/>
+      <c r="C689" t="n">
+        <v>1.973904</v>
+      </c>
+      <c r="D689" t="n">
+        <v>-75.93185699999999</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -12481,8 +12833,12 @@
           <t>Villavieja</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
+      <c r="C690" t="n">
+        <v>3.21954</v>
+      </c>
+      <c r="D690" t="n">
+        <v>-75.219026</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -12495,8 +12851,12 @@
           <t>Yaguará</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
+      <c r="C691" t="n">
+        <v>2.662877</v>
+      </c>
+      <c r="D691" t="n">
+        <v>-75.516008</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -12509,8 +12869,12 @@
           <t>Albania</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
+      <c r="C692" t="n">
+        <v>11.157772</v>
+      </c>
+      <c r="D692" t="n">
+        <v>-72.599239</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -12523,8 +12887,12 @@
           <t>Barrancas</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr"/>
+      <c r="C693" t="n">
+        <v>10.954168</v>
+      </c>
+      <c r="D693" t="n">
+        <v>-72.788864</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -12537,8 +12905,12 @@
           <t>Dibulla</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
+      <c r="C694" t="n">
+        <v>11.272246</v>
+      </c>
+      <c r="D694" t="n">
+        <v>-73.31144</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -12551,8 +12923,12 @@
           <t>Distracción</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
+      <c r="C695" t="n">
+        <v>10.911856</v>
+      </c>
+      <c r="D695" t="n">
+        <v>-72.945125</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -12565,8 +12941,12 @@
           <t>El Molino</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr"/>
-      <c r="D696" t="inlineStr"/>
+      <c r="C696" t="n">
+        <v>10.628411</v>
+      </c>
+      <c r="D696" t="n">
+        <v>-72.873093</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -12579,8 +12959,12 @@
           <t>Fonseca</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
+      <c r="C697" t="n">
+        <v>10.886181</v>
+      </c>
+      <c r="D697" t="n">
+        <v>-72.83800599999999</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -12593,8 +12977,12 @@
           <t>Hatonuevo</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
+      <c r="C698" t="n">
+        <v>11.067558</v>
+      </c>
+      <c r="D698" t="n">
+        <v>-72.760081</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -12607,8 +12995,12 @@
           <t>La Jagua del Pilar</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr"/>
+      <c r="C699" t="n">
+        <v>10.510202</v>
+      </c>
+      <c r="D699" t="n">
+        <v>-73.07099599999999</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -12621,8 +13013,12 @@
           <t>Maicao</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr"/>
-      <c r="D700" t="inlineStr"/>
+      <c r="C700" t="n">
+        <v>11.377305</v>
+      </c>
+      <c r="D700" t="n">
+        <v>-72.23876300000001</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -12635,8 +13031,12 @@
           <t>Riohacha</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr"/>
+      <c r="C701" t="n">
+        <v>11.544939</v>
+      </c>
+      <c r="D701" t="n">
+        <v>-72.915052</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -12649,8 +13049,12 @@
           <t>Manuare</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr"/>
-      <c r="D702" t="inlineStr"/>
+      <c r="C702" t="n">
+        <v>11.435412</v>
+      </c>
+      <c r="D702" t="n">
+        <v>-72.900216</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -12663,8 +13067,12 @@
           <t>San Juan del Cesar</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr"/>
-      <c r="D703" t="inlineStr"/>
+      <c r="C703" t="n">
+        <v>10.773531</v>
+      </c>
+      <c r="D703" t="n">
+        <v>-73.00191599999999</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -12677,8 +13085,12 @@
           <t>Uribia</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr"/>
-      <c r="D704" t="inlineStr"/>
+      <c r="C704" t="n">
+        <v>12.184394</v>
+      </c>
+      <c r="D704" t="n">
+        <v>-72.139309</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -12691,8 +13103,12 @@
           <t>Urumita</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
+      <c r="C705" t="n">
+        <v>10.555568</v>
+      </c>
+      <c r="D705" t="n">
+        <v>-73.012513</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -12705,8 +13121,12 @@
           <t>Villanueva</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr"/>
-      <c r="D706" t="inlineStr"/>
+      <c r="C706" t="n">
+        <v>10.590928</v>
+      </c>
+      <c r="D706" t="n">
+        <v>-72.992406</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -12719,8 +13139,12 @@
           <t>Algarrobo</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr"/>
-      <c r="D707" t="inlineStr"/>
+      <c r="C707" t="n">
+        <v>10.191413</v>
+      </c>
+      <c r="D707" t="n">
+        <v>-74.061817</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -12733,8 +13157,12 @@
           <t>Aracataca</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr"/>
+      <c r="C708" t="n">
+        <v>10.590601</v>
+      </c>
+      <c r="D708" t="n">
+        <v>-74.18768</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -12747,8 +13175,12 @@
           <t>Ariguaní</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr"/>
+      <c r="C709" t="n">
+        <v>9.800547</v>
+      </c>
+      <c r="D709" t="n">
+        <v>-74.059955</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -12761,8 +13193,12 @@
           <t>Cerro de San Antonio</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr"/>
+      <c r="C710" t="n">
+        <v>10.326955</v>
+      </c>
+      <c r="D710" t="n">
+        <v>-74.869012</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -12775,8 +13211,12 @@
           <t>Chibolo</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr"/>
-      <c r="D711" t="inlineStr"/>
+      <c r="C711" t="n">
+        <v>10.026936</v>
+      </c>
+      <c r="D711" t="n">
+        <v>-74.620803</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -12789,8 +13229,12 @@
           <t>Ciénaga</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr"/>
-      <c r="D712" t="inlineStr"/>
+      <c r="C712" t="n">
+        <v>11.01079</v>
+      </c>
+      <c r="D712" t="n">
+        <v>-74.251639</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -12803,8 +13247,12 @@
           <t>Concordia</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr"/>
-      <c r="D713" t="inlineStr"/>
+      <c r="C713" t="n">
+        <v>10.25881</v>
+      </c>
+      <c r="D713" t="n">
+        <v>-74.83410600000001</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -12817,8 +13265,12 @@
           <t>El Banco</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr"/>
-      <c r="D714" t="inlineStr"/>
+      <c r="C714" t="n">
+        <v>9.004917000000001</v>
+      </c>
+      <c r="D714" t="n">
+        <v>-73.97384700000001</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -12831,8 +13283,12 @@
           <t>El Piñón</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr"/>
-      <c r="D715" t="inlineStr"/>
+      <c r="C715" t="n">
+        <v>10.404286</v>
+      </c>
+      <c r="D715" t="n">
+        <v>-74.824308</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -12845,8 +13301,12 @@
           <t>Santa Marta</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
+      <c r="C716" t="n">
+        <v>11.232094</v>
+      </c>
+      <c r="D716" t="n">
+        <v>-74.195092</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -12859,8 +13319,12 @@
           <t>El Retén</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
+      <c r="C717" t="n">
+        <v>10.612076</v>
+      </c>
+      <c r="D717" t="n">
+        <v>-74.269527</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -12873,8 +13337,12 @@
           <t>Fundación</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
+      <c r="C718" t="n">
+        <v>10.515567</v>
+      </c>
+      <c r="D718" t="n">
+        <v>-74.19010900000001</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -12887,8 +13355,12 @@
           <t>Guamal</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
+      <c r="C719" t="n">
+        <v>9.144026</v>
+      </c>
+      <c r="D719" t="n">
+        <v>-74.22366</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -12901,8 +13373,12 @@
           <t>Nueva Granada</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
+      <c r="C720" t="n">
+        <v>9.801819999999999</v>
+      </c>
+      <c r="D720" t="n">
+        <v>-74.39237900000001</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -12915,8 +13391,12 @@
           <t>Pedraza</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
+      <c r="C721" t="n">
+        <v>10.19017</v>
+      </c>
+      <c r="D721" t="n">
+        <v>-74.914171</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -12929,8 +13409,12 @@
           <t>Pijiño del Carmen</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
+      <c r="C722" t="n">
+        <v>9.330422</v>
+      </c>
+      <c r="D722" t="n">
+        <v>-74.45351700000001</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -12943,8 +13427,12 @@
           <t>Pivijay</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
+      <c r="C723" t="n">
+        <v>10.465403</v>
+      </c>
+      <c r="D723" t="n">
+        <v>-74.61696000000001</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -12957,8 +13445,12 @@
           <t>Plato</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr"/>
+      <c r="C724" t="n">
+        <v>9.790416</v>
+      </c>
+      <c r="D724" t="n">
+        <v>-74.78200200000001</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -12971,8 +13463,12 @@
           <t>Pueblo Viejo</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
-      <c r="D725" t="inlineStr"/>
+      <c r="C725" t="n">
+        <v>10.787692</v>
+      </c>
+      <c r="D725" t="n">
+        <v>-73.918391</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -12985,8 +13481,12 @@
           <t>Remolino</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr"/>
+      <c r="C726" t="n">
+        <v>10.702015</v>
+      </c>
+      <c r="D726" t="n">
+        <v>-74.717011</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -12999,8 +13499,12 @@
           <t>Sabanas de San Ángel</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr"/>
+      <c r="C727" t="n">
+        <v>10.13218</v>
+      </c>
+      <c r="D727" t="n">
+        <v>-74.2534</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -13013,8 +13517,12 @@
           <t>Salamina</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
+      <c r="C728" t="n">
+        <v>10.490258</v>
+      </c>
+      <c r="D728" t="n">
+        <v>-74.793778</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -13027,8 +13535,12 @@
           <t>San Sebastián de Buenavista</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr"/>
+      <c r="C729" t="n">
+        <v>9.239758</v>
+      </c>
+      <c r="D729" t="n">
+        <v>-74.35155399999999</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -13041,8 +13553,12 @@
           <t>Santa Ana</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr"/>
-      <c r="D730" t="inlineStr"/>
+      <c r="C730" t="n">
+        <v>9.322903999999999</v>
+      </c>
+      <c r="D730" t="n">
+        <v>-74.56965700000001</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -13055,8 +13571,12 @@
           <t>Santa Bárbara de Pinto</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr"/>
-      <c r="D731" t="inlineStr"/>
+      <c r="C731" t="n">
+        <v>9.431657</v>
+      </c>
+      <c r="D731" t="n">
+        <v>-74.70475</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -13069,8 +13589,12 @@
           <t>San Zenón</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr"/>
+      <c r="C732" t="n">
+        <v>9.355002000000001</v>
+      </c>
+      <c r="D732" t="n">
+        <v>-74.276319</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -13083,8 +13607,12 @@
           <t>Sitionuevo</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr"/>
-      <c r="D733" t="inlineStr"/>
+      <c r="C733" t="n">
+        <v>10.777001</v>
+      </c>
+      <c r="D733" t="n">
+        <v>-74.72060399999999</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -13097,8 +13625,12 @@
           <t>Tenerife</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr"/>
-      <c r="D734" t="inlineStr"/>
+      <c r="C734" t="n">
+        <v>9.900349</v>
+      </c>
+      <c r="D734" t="n">
+        <v>-74.858997</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -13111,8 +13643,12 @@
           <t>Zapayán</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr"/>
+      <c r="C735" t="n">
+        <v>10.136814</v>
+      </c>
+      <c r="D735" t="n">
+        <v>-74.68730100000001</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -13125,8 +13661,12 @@
           <t>Zona Bananera</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr"/>
-      <c r="D736" t="inlineStr"/>
+      <c r="C736" t="n">
+        <v>10.796809</v>
+      </c>
+      <c r="D736" t="n">
+        <v>-74.18079</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -13139,8 +13679,12 @@
           <t>Acacías</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr"/>
+      <c r="C737" t="n">
+        <v>3.988732</v>
+      </c>
+      <c r="D737" t="n">
+        <v>-73.767432</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -13153,8 +13697,12 @@
           <t>Barranca de Upía</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr"/>
-      <c r="D738" t="inlineStr"/>
+      <c r="C738" t="n">
+        <v>4.570739</v>
+      </c>
+      <c r="D738" t="n">
+        <v>-72.963415</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -13167,8 +13715,12 @@
           <t>Cabuyaro</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr"/>
-      <c r="D739" t="inlineStr"/>
+      <c r="C739" t="n">
+        <v>4.288766</v>
+      </c>
+      <c r="D739" t="n">
+        <v>-72.78989</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -13181,8 +13733,12 @@
           <t>Castilla La Nueva</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr"/>
-      <c r="D740" t="inlineStr"/>
+      <c r="C740" t="n">
+        <v>3.827534</v>
+      </c>
+      <c r="D740" t="n">
+        <v>-73.68928</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -13195,8 +13751,12 @@
           <t>Cubarral</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
-      <c r="D741" t="inlineStr"/>
+      <c r="C741" t="n">
+        <v>3.794316</v>
+      </c>
+      <c r="D741" t="n">
+        <v>-73.839038</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -13209,8 +13769,12 @@
           <t>Cumaral</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr"/>
-      <c r="D742" t="inlineStr"/>
+      <c r="C742" t="n">
+        <v>4.271167</v>
+      </c>
+      <c r="D742" t="n">
+        <v>-73.487769</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -13223,8 +13787,12 @@
           <t>El Calvario</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr"/>
-      <c r="D743" t="inlineStr"/>
+      <c r="C743" t="n">
+        <v>4.35182</v>
+      </c>
+      <c r="D743" t="n">
+        <v>-73.714662</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -13237,8 +13805,12 @@
           <t>El Castillo</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr"/>
-      <c r="D744" t="inlineStr"/>
+      <c r="C744" t="n">
+        <v>3.564796</v>
+      </c>
+      <c r="D744" t="n">
+        <v>-73.794291</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -13251,8 +13823,12 @@
           <t>El Dorado</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr"/>
-      <c r="D745" t="inlineStr"/>
+      <c r="C745" t="n">
+        <v>3.739351</v>
+      </c>
+      <c r="D745" t="n">
+        <v>-73.835054</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -13265,8 +13841,12 @@
           <t>Villavicencio</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr"/>
-      <c r="D746" t="inlineStr"/>
+      <c r="C746" t="n">
+        <v>4.134764</v>
+      </c>
+      <c r="D746" t="n">
+        <v>-73.620152</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -13279,8 +13859,12 @@
           <t>Fuente de Oro</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr"/>
-      <c r="D747" t="inlineStr"/>
+      <c r="C747" t="n">
+        <v>3.46395</v>
+      </c>
+      <c r="D747" t="n">
+        <v>-73.621396</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -13293,8 +13877,12 @@
           <t>Granada</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr"/>
+      <c r="C748" t="n">
+        <v>3.548259</v>
+      </c>
+      <c r="D748" t="n">
+        <v>-73.705117</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -13307,8 +13895,12 @@
           <t>Guamal</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr"/>
-      <c r="D749" t="inlineStr"/>
+      <c r="C749" t="n">
+        <v>3.877268</v>
+      </c>
+      <c r="D749" t="n">
+        <v>-73.77014200000001</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -13321,8 +13913,12 @@
           <t>La Macarena</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
+      <c r="C750" t="n">
+        <v>2.304575</v>
+      </c>
+      <c r="D750" t="n">
+        <v>-73.840405</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -13335,8 +13931,12 @@
           <t>La Uribe</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr"/>
+      <c r="C751" t="n">
+        <v>3.24133</v>
+      </c>
+      <c r="D751" t="n">
+        <v>-74.351066</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -13349,8 +13949,12 @@
           <t>Lejanías</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
+      <c r="C752" t="n">
+        <v>3.52651</v>
+      </c>
+      <c r="D752" t="n">
+        <v>-74.022623</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -13363,8 +13967,12 @@
           <t>Mapiripán</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr"/>
+      <c r="C753" t="n">
+        <v>2.893396</v>
+      </c>
+      <c r="D753" t="n">
+        <v>-72.132043</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -13377,8 +13985,12 @@
           <t>Mesetas</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr"/>
+      <c r="C754" t="n">
+        <v>3.384028</v>
+      </c>
+      <c r="D754" t="n">
+        <v>-74.04386599999999</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -13391,8 +14003,12 @@
           <t>Puerto Gaitán</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr"/>
+      <c r="C755" t="n">
+        <v>4.312072</v>
+      </c>
+      <c r="D755" t="n">
+        <v>-72.08295099999999</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -13405,8 +14021,12 @@
           <t>Puerto Lleras</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr"/>
+      <c r="C756" t="n">
+        <v>3.269728</v>
+      </c>
+      <c r="D756" t="n">
+        <v>-73.375602</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -13419,8 +14039,12 @@
           <t>Puerto López</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
+      <c r="C757" t="n">
+        <v>4.085013</v>
+      </c>
+      <c r="D757" t="n">
+        <v>-72.958467</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -13433,8 +14057,12 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr"/>
-      <c r="D758" t="inlineStr"/>
+      <c r="C758" t="n">
+        <v>2.940212</v>
+      </c>
+      <c r="D758" t="n">
+        <v>-73.205134</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -13447,8 +14075,12 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr"/>
-      <c r="D759" t="inlineStr"/>
+      <c r="C759" t="n">
+        <v>4.259727</v>
+      </c>
+      <c r="D759" t="n">
+        <v>-73.565484</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -13461,8 +14093,12 @@
           <t>San Carlos de Guaroa</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr"/>
+      <c r="C760" t="n">
+        <v>3.835189</v>
+      </c>
+      <c r="D760" t="n">
+        <v>-73.259844</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -13475,8 +14111,12 @@
           <t>San Juan de Arama</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr"/>
+      <c r="C761" t="n">
+        <v>3.371208</v>
+      </c>
+      <c r="D761" t="n">
+        <v>-73.872193</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -13489,8 +14129,12 @@
           <t>San Juanito</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
+      <c r="C762" t="n">
+        <v>4.458563</v>
+      </c>
+      <c r="D762" t="n">
+        <v>-73.67715800000001</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -13503,8 +14147,12 @@
           <t>San Martín</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr"/>
+      <c r="C763" t="n">
+        <v>3.69439</v>
+      </c>
+      <c r="D763" t="n">
+        <v>-73.695291</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -13517,8 +14165,12 @@
           <t>Vista Hermosa</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
+      <c r="C764" t="n">
+        <v>2.769394</v>
+      </c>
+      <c r="D764" t="n">
+        <v>-73.69275500000001</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -13531,8 +14183,12 @@
           <t>Albán</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
+      <c r="C765" t="n">
+        <v>1.474437</v>
+      </c>
+      <c r="D765" t="n">
+        <v>-77.08134099999999</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -13545,8 +14201,12 @@
           <t>Aldana</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
+      <c r="C766" t="n">
+        <v>0.882255</v>
+      </c>
+      <c r="D766" t="n">
+        <v>-77.700316</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -13559,8 +14219,12 @@
           <t>Ancuya</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
+      <c r="C767" t="n">
+        <v>1.261528</v>
+      </c>
+      <c r="D767" t="n">
+        <v>-77.514748</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -13573,8 +14237,12 @@
           <t>Arboleda</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr"/>
+      <c r="C768" t="n">
+        <v>1.343603</v>
+      </c>
+      <c r="D768" t="n">
+        <v>-77.533083</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -13587,8 +14255,12 @@
           <t>Barbacoas</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
+      <c r="C769" t="n">
+        <v>1.674104</v>
+      </c>
+      <c r="D769" t="n">
+        <v>-78.136495</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -13601,8 +14273,12 @@
           <t>Belén</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr"/>
+      <c r="C770" t="n">
+        <v>1.596116</v>
+      </c>
+      <c r="D770" t="n">
+        <v>-77.015936</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -13615,8 +14291,12 @@
           <t>Buesaco</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr"/>
+      <c r="C771" t="n">
+        <v>1.384101</v>
+      </c>
+      <c r="D771" t="n">
+        <v>-77.15661900000001</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -13629,8 +14309,12 @@
           <t>Chachagüí</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr"/>
-      <c r="D772" t="inlineStr"/>
+      <c r="C772" t="n">
+        <v>1.396946</v>
+      </c>
+      <c r="D772" t="n">
+        <v>-77.290994</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -13643,8 +14327,12 @@
           <t>Colón</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr"/>
-      <c r="D773" t="inlineStr"/>
+      <c r="C773" t="n">
+        <v>1.631047</v>
+      </c>
+      <c r="D773" t="n">
+        <v>-77.036321</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -13657,8 +14345,12 @@
           <t>Pasto</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr"/>
-      <c r="D774" t="inlineStr"/>
+      <c r="C774" t="n">
+        <v>1.214028</v>
+      </c>
+      <c r="D774" t="n">
+        <v>-77.27851</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -13671,8 +14363,12 @@
           <t>Consacá</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr"/>
-      <c r="D775" t="inlineStr"/>
+      <c r="C775" t="n">
+        <v>1.209297</v>
+      </c>
+      <c r="D775" t="n">
+        <v>-77.42671900000001</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -13685,8 +14381,12 @@
           <t>Contadero</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr"/>
-      <c r="D776" t="inlineStr"/>
+      <c r="C776" t="n">
+        <v>0.927503</v>
+      </c>
+      <c r="D776" t="n">
+        <v>-77.521693</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -13699,8 +14399,12 @@
           <t>Córdoba</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr"/>
-      <c r="D777" t="inlineStr"/>
+      <c r="C777" t="n">
+        <v>0.85407</v>
+      </c>
+      <c r="D777" t="n">
+        <v>-77.518259</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -13713,8 +14417,12 @@
           <t>Cuaspud</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr"/>
-      <c r="D778" t="inlineStr"/>
+      <c r="C778" t="n">
+        <v>0.875091</v>
+      </c>
+      <c r="D778" t="n">
+        <v>-77.74201100000001</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -13727,8 +14435,12 @@
           <t>Cumbal</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr"/>
-      <c r="D779" t="inlineStr"/>
+      <c r="C779" t="n">
+        <v>0.909208</v>
+      </c>
+      <c r="D779" t="n">
+        <v>-77.788906</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -13741,8 +14453,12 @@
           <t>Cumbitara</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr"/>
+      <c r="C780" t="n">
+        <v>1.647362</v>
+      </c>
+      <c r="D780" t="n">
+        <v>-77.57809399999999</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -13755,8 +14471,12 @@
           <t>El Charco</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr"/>
+      <c r="C781" t="n">
+        <v>2.479821</v>
+      </c>
+      <c r="D781" t="n">
+        <v>-78.110793</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -13769,8 +14489,12 @@
           <t>El Peñol</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr"/>
-      <c r="D782" t="inlineStr"/>
+      <c r="C782" t="n">
+        <v>1.454125</v>
+      </c>
+      <c r="D782" t="n">
+        <v>-77.439666</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -13783,8 +14507,12 @@
           <t>El Rosario</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr"/>
-      <c r="D783" t="inlineStr"/>
+      <c r="C783" t="n">
+        <v>1.742624</v>
+      </c>
+      <c r="D783" t="n">
+        <v>-77.334965</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -13797,8 +14525,12 @@
           <t>El Tablón de Gómez</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr"/>
-      <c r="D784" t="inlineStr"/>
+      <c r="C784" t="n">
+        <v>1.637797</v>
+      </c>
+      <c r="D784" t="n">
+        <v>-76.95962400000001</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -13811,8 +14543,12 @@
           <t>El Tambo</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr"/>
-      <c r="D785" t="inlineStr"/>
+      <c r="C785" t="n">
+        <v>1.409312</v>
+      </c>
+      <c r="D785" t="n">
+        <v>-77.392331</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -13825,8 +14561,12 @@
           <t>Francisco Pizarro</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr"/>
-      <c r="D786" t="inlineStr"/>
+      <c r="C786" t="n">
+        <v>2.08652</v>
+      </c>
+      <c r="D786" t="n">
+        <v>-78.59791199999999</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -13839,8 +14579,12 @@
           <t>Funes</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr"/>
-      <c r="D787" t="inlineStr"/>
+      <c r="C787" t="n">
+        <v>0.99873</v>
+      </c>
+      <c r="D787" t="n">
+        <v>-77.448542</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -13853,8 +14597,12 @@
           <t>Guachucal</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr"/>
-      <c r="D788" t="inlineStr"/>
+      <c r="C788" t="n">
+        <v>0.9573430000000001</v>
+      </c>
+      <c r="D788" t="n">
+        <v>-77.733358</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -13867,8 +14615,12 @@
           <t>Guaitarilla</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr"/>
-      <c r="D789" t="inlineStr"/>
+      <c r="C789" t="n">
+        <v>1.130524</v>
+      </c>
+      <c r="D789" t="n">
+        <v>-77.54834200000001</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -13881,8 +14633,12 @@
           <t>Gualmatán</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr"/>
-      <c r="D790" t="inlineStr"/>
+      <c r="C790" t="n">
+        <v>0.920021</v>
+      </c>
+      <c r="D790" t="n">
+        <v>-77.566138</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -13895,8 +14651,12 @@
           <t>Iles</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr"/>
-      <c r="D791" t="inlineStr"/>
+      <c r="C791" t="n">
+        <v>0.96983</v>
+      </c>
+      <c r="D791" t="n">
+        <v>-77.52016399999999</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -13909,8 +14669,12 @@
           <t>Imués</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr"/>
-      <c r="D792" t="inlineStr"/>
+      <c r="C792" t="n">
+        <v>1.069375</v>
+      </c>
+      <c r="D792" t="n">
+        <v>-77.504296</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -13923,8 +14687,12 @@
           <t>Ipiales</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr"/>
-      <c r="D793" t="inlineStr"/>
+      <c r="C793" t="n">
+        <v>0.82365</v>
+      </c>
+      <c r="D793" t="n">
+        <v>-77.634856</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -13937,8 +14705,12 @@
           <t>La Cruz</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr"/>
-      <c r="D794" t="inlineStr"/>
+      <c r="C794" t="n">
+        <v>1.600335</v>
+      </c>
+      <c r="D794" t="n">
+        <v>-76.97116699999999</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -13951,8 +14723,12 @@
           <t>La Florida</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr"/>
-      <c r="D795" t="inlineStr"/>
+      <c r="C795" t="n">
+        <v>1.298607</v>
+      </c>
+      <c r="D795" t="n">
+        <v>-77.404484</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -13965,8 +14741,12 @@
           <t>La Llanada</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr"/>
-      <c r="D796" t="inlineStr"/>
+      <c r="C796" t="n">
+        <v>1.472721</v>
+      </c>
+      <c r="D796" t="n">
+        <v>-77.580202</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -13979,8 +14759,12 @@
           <t>La Tola</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr"/>
-      <c r="D797" t="inlineStr"/>
+      <c r="C797" t="n">
+        <v>2.399579</v>
+      </c>
+      <c r="D797" t="n">
+        <v>-78.188293</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -13993,8 +14777,12 @@
           <t>La Unión</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr"/>
-      <c r="D798" t="inlineStr"/>
+      <c r="C798" t="n">
+        <v>1.598998</v>
+      </c>
+      <c r="D798" t="n">
+        <v>-77.1306</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -14007,8 +14795,12 @@
           <t>Leiva</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr"/>
-      <c r="D799" t="inlineStr"/>
+      <c r="C799" t="n">
+        <v>1.935606</v>
+      </c>
+      <c r="D799" t="n">
+        <v>-77.306819</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -14021,8 +14813,12 @@
           <t>Linares</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr"/>
-      <c r="D800" t="inlineStr"/>
+      <c r="C800" t="n">
+        <v>1.351646</v>
+      </c>
+      <c r="D800" t="n">
+        <v>-77.523517</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -14035,8 +14831,12 @@
           <t>Los Andes</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr"/>
-      <c r="D801" t="inlineStr"/>
+      <c r="C801" t="n">
+        <v>1.493279</v>
+      </c>
+      <c r="D801" t="n">
+        <v>-77.521055</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -14049,8 +14849,12 @@
           <t>Magüí Payán</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr"/>
-      <c r="D802" t="inlineStr"/>
+      <c r="C802" t="n">
+        <v>1.766577</v>
+      </c>
+      <c r="D802" t="n">
+        <v>-78.183571</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -14063,8 +14867,12 @@
           <t>Mallama</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr"/>
-      <c r="D803" t="inlineStr"/>
+      <c r="C803" t="n">
+        <v>1.188997</v>
+      </c>
+      <c r="D803" t="n">
+        <v>-77.870565</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -14077,8 +14885,12 @@
           <t>Mosquera</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr"/>
-      <c r="D804" t="inlineStr"/>
+      <c r="C804" t="n">
+        <v>2.507865</v>
+      </c>
+      <c r="D804" t="n">
+        <v>-78.451646</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -14091,8 +14903,12 @@
           <t>Nariño</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr"/>
-      <c r="D805" t="inlineStr"/>
+      <c r="C805" t="n">
+        <v>1.584227</v>
+      </c>
+      <c r="D805" t="n">
+        <v>-77.858577</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -14105,8 +14921,12 @@
           <t>Olaya Herrera</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr"/>
-      <c r="D806" t="inlineStr"/>
+      <c r="C806" t="n">
+        <v>2.310128</v>
+      </c>
+      <c r="D806" t="n">
+        <v>-78.30421</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -14119,8 +14939,12 @@
           <t>Ospina</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr"/>
-      <c r="D807" t="inlineStr"/>
+      <c r="C807" t="n">
+        <v>1.058653</v>
+      </c>
+      <c r="D807" t="n">
+        <v>-77.56567</v>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -14133,8 +14957,12 @@
           <t>Policarpa</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr"/>
-      <c r="D808" t="inlineStr"/>
+      <c r="C808" t="n">
+        <v>1.628664</v>
+      </c>
+      <c r="D808" t="n">
+        <v>-77.45946499999999</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -14147,8 +14975,12 @@
           <t>Potosí</t>
         </is>
       </c>
-      <c r="C809" t="inlineStr"/>
-      <c r="D809" t="inlineStr"/>
+      <c r="C809" t="n">
+        <v>0.734017</v>
+      </c>
+      <c r="D809" t="n">
+        <v>-77.409177</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -14161,8 +14993,12 @@
           <t>Providencia</t>
         </is>
       </c>
-      <c r="C810" t="inlineStr"/>
-      <c r="D810" t="inlineStr"/>
+      <c r="C810" t="n">
+        <v>1.239193</v>
+      </c>
+      <c r="D810" t="n">
+        <v>-77.59736599999999</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -14175,8 +15011,12 @@
           <t>Puerres</t>
         </is>
       </c>
-      <c r="C811" t="inlineStr"/>
-      <c r="D811" t="inlineStr"/>
+      <c r="C811" t="n">
+        <v>0.799616</v>
+      </c>
+      <c r="D811" t="n">
+        <v>-77.25644699999999</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -14189,8 +15029,12 @@
           <t>Pupiales</t>
         </is>
       </c>
-      <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr"/>
+      <c r="C812" t="n">
+        <v>0.870797</v>
+      </c>
+      <c r="D812" t="n">
+        <v>-77.641936</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -14203,8 +15047,12 @@
           <t>Ricaurte</t>
         </is>
       </c>
-      <c r="C813" t="inlineStr"/>
-      <c r="D813" t="inlineStr"/>
+      <c r="C813" t="n">
+        <v>1.213249</v>
+      </c>
+      <c r="D813" t="n">
+        <v>-77.994501</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -14217,8 +15065,12 @@
           <t>Roberto Payán</t>
         </is>
       </c>
-      <c r="C814" t="inlineStr"/>
-      <c r="D814" t="inlineStr"/>
+      <c r="C814" t="n">
+        <v>1.869344</v>
+      </c>
+      <c r="D814" t="n">
+        <v>-78.369429</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -14231,8 +15083,12 @@
           <t>Samaniego</t>
         </is>
       </c>
-      <c r="C815" t="inlineStr"/>
-      <c r="D815" t="inlineStr"/>
+      <c r="C815" t="n">
+        <v>1.338952</v>
+      </c>
+      <c r="D815" t="n">
+        <v>-77.593379</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -14245,8 +15101,12 @@
           <t>San Bernardo</t>
         </is>
       </c>
-      <c r="C816" t="inlineStr"/>
-      <c r="D816" t="inlineStr"/>
+      <c r="C816" t="n">
+        <v>1.515875</v>
+      </c>
+      <c r="D816" t="n">
+        <v>-77.045772</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -14259,8 +15119,12 @@
           <t>San Lorenzo</t>
         </is>
       </c>
-      <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr"/>
+      <c r="C817" t="n">
+        <v>1.503155</v>
+      </c>
+      <c r="D817" t="n">
+        <v>-77.21533700000001</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -14273,8 +15137,12 @@
           <t>San Pablo</t>
         </is>
       </c>
-      <c r="C818" t="inlineStr"/>
-      <c r="D818" t="inlineStr"/>
+      <c r="C818" t="n">
+        <v>1.678862</v>
+      </c>
+      <c r="D818" t="n">
+        <v>-76.98917400000001</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -14287,8 +15155,12 @@
           <t>San Pedro de Cartago</t>
         </is>
       </c>
-      <c r="C819" t="inlineStr"/>
-      <c r="D819" t="inlineStr"/>
+      <c r="C819" t="n">
+        <v>1.55249</v>
+      </c>
+      <c r="D819" t="n">
+        <v>-77.120017</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -14301,8 +15173,12 @@
           <t>Sandoná</t>
         </is>
       </c>
-      <c r="C820" t="inlineStr"/>
-      <c r="D820" t="inlineStr"/>
+      <c r="C820" t="n">
+        <v>1.286384</v>
+      </c>
+      <c r="D820" t="n">
+        <v>-77.47107200000001</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -14315,8 +15191,12 @@
           <t>Santa Bárbara</t>
         </is>
       </c>
-      <c r="C821" t="inlineStr"/>
-      <c r="D821" t="inlineStr"/>
+      <c r="C821" t="n">
+        <v>2.32421</v>
+      </c>
+      <c r="D821" t="n">
+        <v>-77.927314</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -14329,8 +15209,12 @@
           <t>Santacruz</t>
         </is>
       </c>
-      <c r="C822" t="inlineStr"/>
-      <c r="D822" t="inlineStr"/>
+      <c r="C822" t="n">
+        <v>1.222683</v>
+      </c>
+      <c r="D822" t="n">
+        <v>-77.676969</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -14343,8 +15227,12 @@
           <t>Sapuyes</t>
         </is>
       </c>
-      <c r="C823" t="inlineStr"/>
-      <c r="D823" t="inlineStr"/>
+      <c r="C823" t="n">
+        <v>1.03772</v>
+      </c>
+      <c r="D823" t="n">
+        <v>-77.620919</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -14357,8 +15245,12 @@
           <t>Taminango</t>
         </is>
       </c>
-      <c r="C824" t="inlineStr"/>
-      <c r="D824" t="inlineStr"/>
+      <c r="C824" t="n">
+        <v>1.569622</v>
+      </c>
+      <c r="D824" t="n">
+        <v>-77.27729600000001</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -14371,8 +15263,12 @@
           <t>Tangua</t>
         </is>
       </c>
-      <c r="C825" t="inlineStr"/>
-      <c r="D825" t="inlineStr"/>
+      <c r="C825" t="n">
+        <v>1.094402</v>
+      </c>
+      <c r="D825" t="n">
+        <v>-77.39480500000001</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -14385,8 +15281,12 @@
           <t>Tumaco</t>
         </is>
       </c>
-      <c r="C826" t="inlineStr"/>
-      <c r="D826" t="inlineStr"/>
+      <c r="C826" t="n">
+        <v>1.806289</v>
+      </c>
+      <c r="D826" t="n">
+        <v>-78.76498100000001</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -14399,8 +15299,12 @@
           <t>Túquerres</t>
         </is>
       </c>
-      <c r="C827" t="inlineStr"/>
-      <c r="D827" t="inlineStr"/>
+      <c r="C827" t="n">
+        <v>1.087702</v>
+      </c>
+      <c r="D827" t="n">
+        <v>-77.618824</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -14413,8 +15317,12 @@
           <t>Yacuanquer</t>
         </is>
       </c>
-      <c r="C828" t="inlineStr"/>
-      <c r="D828" t="inlineStr"/>
+      <c r="C828" t="n">
+        <v>1.115882</v>
+      </c>
+      <c r="D828" t="n">
+        <v>-77.40175600000001</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -14427,8 +15335,12 @@
           <t>Ábrego</t>
         </is>
       </c>
-      <c r="C829" t="inlineStr"/>
-      <c r="D829" t="inlineStr"/>
+      <c r="C829" t="n">
+        <v>8.081889</v>
+      </c>
+      <c r="D829" t="n">
+        <v>-73.220872</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -14441,8 +15353,12 @@
           <t>Arboledas</t>
         </is>
       </c>
-      <c r="C830" t="inlineStr"/>
-      <c r="D830" t="inlineStr"/>
+      <c r="C830" t="n">
+        <v>7.642726</v>
+      </c>
+      <c r="D830" t="n">
+        <v>-72.799341</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -14455,8 +15371,12 @@
           <t>Bochalema</t>
         </is>
       </c>
-      <c r="C831" t="inlineStr"/>
-      <c r="D831" t="inlineStr"/>
+      <c r="C831" t="n">
+        <v>7.61236</v>
+      </c>
+      <c r="D831" t="n">
+        <v>-72.647143</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -14469,8 +15389,12 @@
           <t>Bucarasica</t>
         </is>
       </c>
-      <c r="C832" t="inlineStr"/>
-      <c r="D832" t="inlineStr"/>
+      <c r="C832" t="n">
+        <v>8.039486999999999</v>
+      </c>
+      <c r="D832" t="n">
+        <v>-72.866947</v>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -14483,8 +15407,12 @@
           <t>Cáchira</t>
         </is>
       </c>
-      <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr"/>
+      <c r="C833" t="n">
+        <v>7.7419</v>
+      </c>
+      <c r="D833" t="n">
+        <v>-73.048523</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -14497,8 +15425,12 @@
           <t>Cácota</t>
         </is>
       </c>
-      <c r="C834" t="inlineStr"/>
-      <c r="D834" t="inlineStr"/>
+      <c r="C834" t="n">
+        <v>7.268454</v>
+      </c>
+      <c r="D834" t="n">
+        <v>-72.641965</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -14511,8 +15443,12 @@
           <t>Chinácota</t>
         </is>
       </c>
-      <c r="C835" t="inlineStr"/>
-      <c r="D835" t="inlineStr"/>
+      <c r="C835" t="n">
+        <v>7.608411</v>
+      </c>
+      <c r="D835" t="n">
+        <v>-72.600268</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -14525,8 +15461,12 @@
           <t>Chitagá</t>
         </is>
       </c>
-      <c r="C836" t="inlineStr"/>
-      <c r="D836" t="inlineStr"/>
+      <c r="C836" t="n">
+        <v>7.13819</v>
+      </c>
+      <c r="D836" t="n">
+        <v>-72.664795</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -14539,8 +15479,12 @@
           <t>Convención</t>
         </is>
       </c>
-      <c r="C837" t="inlineStr"/>
-      <c r="D837" t="inlineStr"/>
+      <c r="C837" t="n">
+        <v>8.466253999999999</v>
+      </c>
+      <c r="D837" t="n">
+        <v>-73.336219</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -14553,8 +15497,12 @@
           <t>Cúcuta</t>
         </is>
       </c>
-      <c r="C838" t="inlineStr"/>
-      <c r="D838" t="inlineStr"/>
+      <c r="C838" t="n">
+        <v>7.897146</v>
+      </c>
+      <c r="D838" t="n">
+        <v>-72.508039</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -14567,8 +15515,12 @@
           <t>Cucutilla</t>
         </is>
       </c>
-      <c r="C839" t="inlineStr"/>
-      <c r="D839" t="inlineStr"/>
+      <c r="C839" t="n">
+        <v>7.539501</v>
+      </c>
+      <c r="D839" t="n">
+        <v>-72.77276000000001</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -14581,8 +15533,12 @@
           <t>Durania</t>
         </is>
       </c>
-      <c r="C840" t="inlineStr"/>
-      <c r="D840" t="inlineStr"/>
+      <c r="C840" t="n">
+        <v>7.714173</v>
+      </c>
+      <c r="D840" t="n">
+        <v>-72.656694</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -14595,8 +15551,12 @@
           <t>El Carmen</t>
         </is>
       </c>
-      <c r="C841" t="inlineStr"/>
-      <c r="D841" t="inlineStr"/>
+      <c r="C841" t="n">
+        <v>8.168511000000001</v>
+      </c>
+      <c r="D841" t="n">
+        <v>-72.811029</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -14609,8 +15569,12 @@
           <t>El Tarra</t>
         </is>
       </c>
-      <c r="C842" t="inlineStr"/>
-      <c r="D842" t="inlineStr"/>
+      <c r="C842" t="n">
+        <v>8.575002</v>
+      </c>
+      <c r="D842" t="n">
+        <v>-73.093968</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -14623,8 +15587,12 @@
           <t>El Zulia</t>
         </is>
       </c>
-      <c r="C843" t="inlineStr"/>
-      <c r="D843" t="inlineStr"/>
+      <c r="C843" t="n">
+        <v>8.095489000000001</v>
+      </c>
+      <c r="D843" t="n">
+        <v>-72.646377</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -14637,8 +15605,12 @@
           <t>Gramalote</t>
         </is>
       </c>
-      <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr"/>
+      <c r="C844" t="n">
+        <v>7.915523</v>
+      </c>
+      <c r="D844" t="n">
+        <v>-72.786597</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -14651,8 +15623,12 @@
           <t>Hacarí</t>
         </is>
       </c>
-      <c r="C845" t="inlineStr"/>
-      <c r="D845" t="inlineStr"/>
+      <c r="C845" t="n">
+        <v>8.32085</v>
+      </c>
+      <c r="D845" t="n">
+        <v>-73.14532699999999</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -14665,8 +15641,12 @@
           <t>Herrán</t>
         </is>
       </c>
-      <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr"/>
+      <c r="C846" t="n">
+        <v>7.506895</v>
+      </c>
+      <c r="D846" t="n">
+        <v>-72.48319499999999</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -14679,8 +15659,12 @@
           <t>La Esperanza</t>
         </is>
       </c>
-      <c r="C847" t="inlineStr"/>
-      <c r="D847" t="inlineStr"/>
+      <c r="C847" t="n">
+        <v>7.69574</v>
+      </c>
+      <c r="D847" t="n">
+        <v>-73.354707</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -14693,8 +15677,12 @@
           <t>La Playa de Belén</t>
         </is>
       </c>
-      <c r="C848" t="inlineStr"/>
-      <c r="D848" t="inlineStr"/>
+      <c r="C848" t="n">
+        <v>8.213727</v>
+      </c>
+      <c r="D848" t="n">
+        <v>-73.238173</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -14707,8 +15695,12 @@
           <t>Labateca</t>
         </is>
       </c>
-      <c r="C849" t="inlineStr"/>
-      <c r="D849" t="inlineStr"/>
+      <c r="C849" t="n">
+        <v>7.299059</v>
+      </c>
+      <c r="D849" t="n">
+        <v>-72.495773</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -14721,8 +15713,12 @@
           <t>Los Patios</t>
         </is>
       </c>
-      <c r="C850" t="inlineStr"/>
-      <c r="D850" t="inlineStr"/>
+      <c r="C850" t="n">
+        <v>7.83422</v>
+      </c>
+      <c r="D850" t="n">
+        <v>-72.50591300000001</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -14735,8 +15731,12 @@
           <t>Lourdes</t>
         </is>
       </c>
-      <c r="C851" t="inlineStr"/>
-      <c r="D851" t="inlineStr"/>
+      <c r="C851" t="n">
+        <v>7.944382</v>
+      </c>
+      <c r="D851" t="n">
+        <v>-72.83347999999999</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -14749,8 +15749,12 @@
           <t>Mutiscua</t>
         </is>
       </c>
-      <c r="C852" t="inlineStr"/>
-      <c r="D852" t="inlineStr"/>
+      <c r="C852" t="n">
+        <v>7.300939</v>
+      </c>
+      <c r="D852" t="n">
+        <v>-72.746724</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -14763,8 +15767,12 @@
           <t>Ocaña</t>
         </is>
       </c>
-      <c r="C853" t="inlineStr"/>
-      <c r="D853" t="inlineStr"/>
+      <c r="C853" t="n">
+        <v>8.235405999999999</v>
+      </c>
+      <c r="D853" t="n">
+        <v>-73.353849</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -14777,8 +15785,12 @@
           <t>Pamplona</t>
         </is>
       </c>
-      <c r="C854" t="inlineStr"/>
-      <c r="D854" t="inlineStr"/>
+      <c r="C854" t="n">
+        <v>7.376381</v>
+      </c>
+      <c r="D854" t="n">
+        <v>-72.648263</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -14791,8 +15803,12 @@
           <t>Pamplonita</t>
         </is>
       </c>
-      <c r="C855" t="inlineStr"/>
-      <c r="D855" t="inlineStr"/>
+      <c r="C855" t="n">
+        <v>7.437016</v>
+      </c>
+      <c r="D855" t="n">
+        <v>-72.63802</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -14805,8 +15821,12 @@
           <t>Puerto Santander</t>
         </is>
       </c>
-      <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr"/>
+      <c r="C856" t="n">
+        <v>8.354657</v>
+      </c>
+      <c r="D856" t="n">
+        <v>-72.414587</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -14819,8 +15839,12 @@
           <t>Ragonvalia</t>
         </is>
       </c>
-      <c r="C857" t="inlineStr"/>
-      <c r="D857" t="inlineStr"/>
+      <c r="C857" t="n">
+        <v>7.577899</v>
+      </c>
+      <c r="D857" t="n">
+        <v>-72.476556</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -14833,8 +15857,12 @@
           <t>Salazar de Las Palmas</t>
         </is>
       </c>
-      <c r="C858" t="inlineStr"/>
-      <c r="D858" t="inlineStr"/>
+      <c r="C858" t="n">
+        <v>7.773214</v>
+      </c>
+      <c r="D858" t="n">
+        <v>-72.816273</v>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -14847,8 +15875,12 @@
           <t>San Calixto</t>
         </is>
       </c>
-      <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr"/>
+      <c r="C859" t="n">
+        <v>8.402898</v>
+      </c>
+      <c r="D859" t="n">
+        <v>-73.207559</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -14861,8 +15893,12 @@
           <t>San Cayetano</t>
         </is>
       </c>
-      <c r="C860" t="inlineStr"/>
-      <c r="D860" t="inlineStr"/>
+      <c r="C860" t="n">
+        <v>7.833353</v>
+      </c>
+      <c r="D860" t="n">
+        <v>-72.61018</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -14875,8 +15911,12 @@
           <t>Santiago</t>
         </is>
       </c>
-      <c r="C861" t="inlineStr"/>
-      <c r="D861" t="inlineStr"/>
+      <c r="C861" t="n">
+        <v>7.864448</v>
+      </c>
+      <c r="D861" t="n">
+        <v>-72.716556</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -14889,8 +15929,12 @@
           <t>Santo Domingo de Silos</t>
         </is>
       </c>
-      <c r="C862" t="inlineStr"/>
-      <c r="D862" t="inlineStr"/>
+      <c r="C862" t="n">
+        <v>42.34711</v>
+      </c>
+      <c r="D862" t="n">
+        <v>-3.693018</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -14903,8 +15947,12 @@
           <t>Sardinata</t>
         </is>
       </c>
-      <c r="C863" t="inlineStr"/>
-      <c r="D863" t="inlineStr"/>
+      <c r="C863" t="n">
+        <v>8.084097</v>
+      </c>
+      <c r="D863" t="n">
+        <v>-72.800066</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -14917,8 +15965,12 @@
           <t>Teorama</t>
         </is>
       </c>
-      <c r="C864" t="inlineStr"/>
-      <c r="D864" t="inlineStr"/>
+      <c r="C864" t="n">
+        <v>8.758691000000001</v>
+      </c>
+      <c r="D864" t="n">
+        <v>-73.160888</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -14931,8 +15983,12 @@
           <t>Tibú</t>
         </is>
       </c>
-      <c r="C865" t="inlineStr"/>
-      <c r="D865" t="inlineStr"/>
+      <c r="C865" t="n">
+        <v>8.637136</v>
+      </c>
+      <c r="D865" t="n">
+        <v>-72.734461</v>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -14945,8 +16001,12 @@
           <t>Toledo</t>
         </is>
       </c>
-      <c r="C866" t="inlineStr"/>
-      <c r="D866" t="inlineStr"/>
+      <c r="C866" t="n">
+        <v>7.310534</v>
+      </c>
+      <c r="D866" t="n">
+        <v>-72.483796</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -14959,8 +16019,12 @@
           <t>Villa Caro</t>
         </is>
       </c>
-      <c r="C867" t="inlineStr"/>
-      <c r="D867" t="inlineStr"/>
+      <c r="C867" t="n">
+        <v>7.913873</v>
+      </c>
+      <c r="D867" t="n">
+        <v>-72.972455</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -14973,8 +16037,12 @@
           <t>Villa del Rosario</t>
         </is>
       </c>
-      <c r="C868" t="inlineStr"/>
-      <c r="D868" t="inlineStr"/>
+      <c r="C868" t="n">
+        <v>7.831893</v>
+      </c>
+      <c r="D868" t="n">
+        <v>-72.471718</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -14987,8 +16055,12 @@
           <t>Colón</t>
         </is>
       </c>
-      <c r="C869" t="inlineStr"/>
-      <c r="D869" t="inlineStr"/>
+      <c r="C869" t="n">
+        <v>1.189491</v>
+      </c>
+      <c r="D869" t="n">
+        <v>-76.97251199999999</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -15001,8 +16073,12 @@
           <t>Orito</t>
         </is>
       </c>
-      <c r="C870" t="inlineStr"/>
-      <c r="D870" t="inlineStr"/>
+      <c r="C870" t="n">
+        <v>0.7390060000000001</v>
+      </c>
+      <c r="D870" t="n">
+        <v>-76.81223900000001</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -15015,8 +16091,12 @@
           <t>Puerto Asís</t>
         </is>
       </c>
-      <c r="C871" t="inlineStr"/>
-      <c r="D871" t="inlineStr"/>
+      <c r="C871" t="n">
+        <v>0.497975</v>
+      </c>
+      <c r="D871" t="n">
+        <v>-76.495142</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -15029,8 +16109,12 @@
           <t>Puerto Caicedo</t>
         </is>
       </c>
-      <c r="C872" t="inlineStr"/>
-      <c r="D872" t="inlineStr"/>
+      <c r="C872" t="n">
+        <v>0.684194</v>
+      </c>
+      <c r="D872" t="n">
+        <v>-76.60441</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -15043,8 +16127,12 @@
           <t>Puerto Guzmán</t>
         </is>
       </c>
-      <c r="C873" t="inlineStr"/>
-      <c r="D873" t="inlineStr"/>
+      <c r="C873" t="n">
+        <v>0.964898</v>
+      </c>
+      <c r="D873" t="n">
+        <v>-76.40783399999999</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -15057,8 +16145,12 @@
           <t>Puerto Leguízamo</t>
         </is>
       </c>
-      <c r="C874" t="inlineStr"/>
-      <c r="D874" t="inlineStr"/>
+      <c r="C874" t="n">
+        <v>-0.194986</v>
+      </c>
+      <c r="D874" t="n">
+        <v>-74.780698</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -15071,8 +16163,12 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="C875" t="inlineStr"/>
-      <c r="D875" t="inlineStr"/>
+      <c r="C875" t="n">
+        <v>1.147838</v>
+      </c>
+      <c r="D875" t="n">
+        <v>-76.8694</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -15085,8 +16181,12 @@
           <t>San Miguel</t>
         </is>
       </c>
-      <c r="C876" t="inlineStr"/>
-      <c r="D876" t="inlineStr"/>
+      <c r="C876" t="n">
+        <v>0.343799</v>
+      </c>
+      <c r="D876" t="n">
+        <v>-76.911006</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -15099,8 +16199,12 @@
           <t>Santiago</t>
         </is>
       </c>
-      <c r="C877" t="inlineStr"/>
-      <c r="D877" t="inlineStr"/>
+      <c r="C877" t="n">
+        <v>1.146773</v>
+      </c>
+      <c r="D877" t="n">
+        <v>-77.002477</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -15113,8 +16217,12 @@
           <t>Mocoa</t>
         </is>
       </c>
-      <c r="C878" t="inlineStr"/>
-      <c r="D878" t="inlineStr"/>
+      <c r="C878" t="n">
+        <v>1.146629</v>
+      </c>
+      <c r="D878" t="n">
+        <v>-76.648233</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -15127,8 +16235,12 @@
           <t>Sibundoy</t>
         </is>
       </c>
-      <c r="C879" t="inlineStr"/>
-      <c r="D879" t="inlineStr"/>
+      <c r="C879" t="n">
+        <v>1.205413</v>
+      </c>
+      <c r="D879" t="n">
+        <v>-76.916004</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -15141,8 +16253,12 @@
           <t>Valle del Guamuez</t>
         </is>
       </c>
-      <c r="C880" t="inlineStr"/>
-      <c r="D880" t="inlineStr"/>
+      <c r="C880" t="n">
+        <v>0.425135</v>
+      </c>
+      <c r="D880" t="n">
+        <v>-76.90371399999999</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -15155,8 +16271,12 @@
           <t>Villagarzón</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr"/>
-      <c r="D881" t="inlineStr"/>
+      <c r="C881" t="n">
+        <v>1.030671</v>
+      </c>
+      <c r="D881" t="n">
+        <v>-76.61691</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -15169,8 +16289,12 @@
           <t>Buenavista</t>
         </is>
       </c>
-      <c r="C882" t="inlineStr"/>
-      <c r="D882" t="inlineStr"/>
+      <c r="C882" t="n">
+        <v>4.3599158</v>
+      </c>
+      <c r="D882" t="n">
+        <v>-75.7386779</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -15183,8 +16307,12 @@
           <t>Calarcá</t>
         </is>
       </c>
-      <c r="C883" t="inlineStr"/>
-      <c r="D883" t="inlineStr"/>
+      <c r="C883" t="n">
+        <v>4.530585</v>
+      </c>
+      <c r="D883" t="n">
+        <v>-75.640632</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -15197,8 +16325,12 @@
           <t>Circasia</t>
         </is>
       </c>
-      <c r="C884" t="inlineStr"/>
-      <c r="D884" t="inlineStr"/>
+      <c r="C884" t="n">
+        <v>4.607567</v>
+      </c>
+      <c r="D884" t="n">
+        <v>-75.666707</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -15211,8 +16343,12 @@
           <t>Córdoba</t>
         </is>
       </c>
-      <c r="C885" t="inlineStr"/>
-      <c r="D885" t="inlineStr"/>
+      <c r="C885" t="n">
+        <v>4.390072</v>
+      </c>
+      <c r="D885" t="n">
+        <v>-75.68582499999999</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -15225,8 +16361,12 @@
           <t>Filandia</t>
         </is>
       </c>
-      <c r="C886" t="inlineStr"/>
-      <c r="D886" t="inlineStr"/>
+      <c r="C886" t="n">
+        <v>4.675077</v>
+      </c>
+      <c r="D886" t="n">
+        <v>-75.657996</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -15239,8 +16379,12 @@
           <t>Génova</t>
         </is>
       </c>
-      <c r="C887" t="inlineStr"/>
-      <c r="D887" t="inlineStr"/>
+      <c r="C887" t="n">
+        <v>4.192992</v>
+      </c>
+      <c r="D887" t="n">
+        <v>-75.744812</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -15253,8 +16397,12 @@
           <t>La Tebaida</t>
         </is>
       </c>
-      <c r="C888" t="inlineStr"/>
-      <c r="D888" t="inlineStr"/>
+      <c r="C888" t="n">
+        <v>4.451218</v>
+      </c>
+      <c r="D888" t="n">
+        <v>-75.788731</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -15267,8 +16415,12 @@
           <t>Montenegro</t>
         </is>
       </c>
-      <c r="C889" t="inlineStr"/>
-      <c r="D889" t="inlineStr"/>
+      <c r="C889" t="n">
+        <v>4.566418</v>
+      </c>
+      <c r="D889" t="n">
+        <v>-75.750708</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -15281,8 +16433,12 @@
           <t>Pijao</t>
         </is>
       </c>
-      <c r="C890" t="inlineStr"/>
-      <c r="D890" t="inlineStr"/>
+      <c r="C890" t="n">
+        <v>4.334144</v>
+      </c>
+      <c r="D890" t="n">
+        <v>-75.703806</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -15295,8 +16451,12 @@
           <t>Armenia</t>
         </is>
       </c>
-      <c r="C891" t="inlineStr"/>
-      <c r="D891" t="inlineStr"/>
+      <c r="C891" t="n">
+        <v>4.536307</v>
+      </c>
+      <c r="D891" t="n">
+        <v>-75.672375</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -15309,8 +16469,12 @@
           <t>Quimbaya</t>
         </is>
       </c>
-      <c r="C892" t="inlineStr"/>
-      <c r="D892" t="inlineStr"/>
+      <c r="C892" t="n">
+        <v>4.623118</v>
+      </c>
+      <c r="D892" t="n">
+        <v>-75.763735</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -15323,8 +16487,12 @@
           <t>Salento</t>
         </is>
       </c>
-      <c r="C893" t="inlineStr"/>
-      <c r="D893" t="inlineStr"/>
+      <c r="C893" t="n">
+        <v>4.710737</v>
+      </c>
+      <c r="D893" t="n">
+        <v>-75.392518</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -15337,8 +16505,12 @@
           <t>Apía</t>
         </is>
       </c>
-      <c r="C894" t="inlineStr"/>
-      <c r="D894" t="inlineStr"/>
+      <c r="C894" t="n">
+        <v>5.106554</v>
+      </c>
+      <c r="D894" t="n">
+        <v>-75.942502</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -15351,8 +16523,12 @@
           <t>Balboa</t>
         </is>
       </c>
-      <c r="C895" t="inlineStr"/>
-      <c r="D895" t="inlineStr"/>
+      <c r="C895" t="n">
+        <v>4.9036</v>
+      </c>
+      <c r="D895" t="n">
+        <v>-75.886306</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -15365,8 +16541,12 @@
           <t>Belén de Umbría</t>
         </is>
       </c>
-      <c r="C896" t="inlineStr"/>
-      <c r="D896" t="inlineStr"/>
+      <c r="C896" t="n">
+        <v>5.200891</v>
+      </c>
+      <c r="D896" t="n">
+        <v>-75.86899200000001</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -15379,8 +16559,12 @@
           <t>Dosquebradas</t>
         </is>
       </c>
-      <c r="C897" t="inlineStr"/>
-      <c r="D897" t="inlineStr"/>
+      <c r="C897" t="n">
+        <v>4.833955</v>
+      </c>
+      <c r="D897" t="n">
+        <v>-75.671301</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -15393,8 +16577,12 @@
           <t>Guática</t>
         </is>
       </c>
-      <c r="C898" t="inlineStr"/>
-      <c r="D898" t="inlineStr"/>
+      <c r="C898" t="n">
+        <v>5.315562</v>
+      </c>
+      <c r="D898" t="n">
+        <v>-75.80080599999999</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -15407,8 +16595,12 @@
           <t>La Celia</t>
         </is>
       </c>
-      <c r="C899" t="inlineStr"/>
-      <c r="D899" t="inlineStr"/>
+      <c r="C899" t="n">
+        <v>5.00335</v>
+      </c>
+      <c r="D899" t="n">
+        <v>-76.003199</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -15421,8 +16613,12 @@
           <t>La Virginia</t>
         </is>
       </c>
-      <c r="C900" t="inlineStr"/>
-      <c r="D900" t="inlineStr"/>
+      <c r="C900" t="n">
+        <v>4.899599</v>
+      </c>
+      <c r="D900" t="n">
+        <v>-75.882566</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -15435,8 +16631,12 @@
           <t>Marsella</t>
         </is>
       </c>
-      <c r="C901" t="inlineStr"/>
-      <c r="D901" t="inlineStr"/>
+      <c r="C901" t="n">
+        <v>4.936758</v>
+      </c>
+      <c r="D901" t="n">
+        <v>-75.73904400000001</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -15449,8 +16649,12 @@
           <t>Mistrató</t>
         </is>
       </c>
-      <c r="C902" t="inlineStr"/>
-      <c r="D902" t="inlineStr"/>
+      <c r="C902" t="n">
+        <v>5.285809</v>
+      </c>
+      <c r="D902" t="n">
+        <v>-75.868589</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -15463,8 +16667,12 @@
           <t>Pereira</t>
         </is>
       </c>
-      <c r="C903" t="inlineStr"/>
-      <c r="D903" t="inlineStr"/>
+      <c r="C903" t="n">
+        <v>4.785461</v>
+      </c>
+      <c r="D903" t="n">
+        <v>-75.78832199999999</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -15477,8 +16685,12 @@
           <t>Pueblo Rico</t>
         </is>
       </c>
-      <c r="C904" t="inlineStr"/>
-      <c r="D904" t="inlineStr"/>
+      <c r="C904" t="n">
+        <v>5.221579</v>
+      </c>
+      <c r="D904" t="n">
+        <v>-76.030216</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -15491,8 +16703,12 @@
           <t>Quinchía</t>
         </is>
       </c>
-      <c r="C905" t="inlineStr"/>
-      <c r="D905" t="inlineStr"/>
+      <c r="C905" t="n">
+        <v>5.326163</v>
+      </c>
+      <c r="D905" t="n">
+        <v>-75.721868</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -15505,8 +16721,12 @@
           <t>Santa Rosa de Cabal</t>
         </is>
       </c>
-      <c r="C906" t="inlineStr"/>
-      <c r="D906" t="inlineStr"/>
+      <c r="C906" t="n">
+        <v>4.865071</v>
+      </c>
+      <c r="D906" t="n">
+        <v>-75.621155</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -15519,8 +16739,12 @@
           <t>Santuario</t>
         </is>
       </c>
-      <c r="C907" t="inlineStr"/>
-      <c r="D907" t="inlineStr"/>
+      <c r="C907" t="n">
+        <v>4.919635</v>
+      </c>
+      <c r="D907" t="n">
+        <v>-75.871719</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -15533,8 +16757,12 @@
           <t>San Andrés</t>
         </is>
       </c>
-      <c r="C908" t="inlineStr"/>
-      <c r="D908" t="inlineStr"/>
+      <c r="C908" t="n">
+        <v>13.353117</v>
+      </c>
+      <c r="D908" t="n">
+        <v>-81.374989</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -15547,8 +16775,12 @@
           <t>Aguada</t>
         </is>
       </c>
-      <c r="C909" t="inlineStr"/>
-      <c r="D909" t="inlineStr"/>
+      <c r="C909" t="n">
+        <v>6.162366</v>
+      </c>
+      <c r="D909" t="n">
+        <v>-73.521569</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -15561,8 +16793,12 @@
           <t>Albania</t>
         </is>
       </c>
-      <c r="C910" t="inlineStr"/>
-      <c r="D910" t="inlineStr"/>
+      <c r="C910" t="n">
+        <v>5.758765</v>
+      </c>
+      <c r="D910" t="n">
+        <v>-73.915162</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -15575,8 +16811,12 @@
           <t>Aratoca</t>
         </is>
       </c>
-      <c r="C911" t="inlineStr"/>
-      <c r="D911" t="inlineStr"/>
+      <c r="C911" t="n">
+        <v>6.694573</v>
+      </c>
+      <c r="D911" t="n">
+        <v>-73.018703</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -15589,8 +16829,12 @@
           <t>Barbosa</t>
         </is>
       </c>
-      <c r="C912" t="inlineStr"/>
-      <c r="D912" t="inlineStr"/>
+      <c r="C912" t="n">
+        <v>5.932603</v>
+      </c>
+      <c r="D912" t="n">
+        <v>-73.612437</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -15603,8 +16847,12 @@
           <t>Barichara</t>
         </is>
       </c>
-      <c r="C913" t="inlineStr"/>
-      <c r="D913" t="inlineStr"/>
+      <c r="C913" t="n">
+        <v>6.635716</v>
+      </c>
+      <c r="D913" t="n">
+        <v>-73.22344200000001</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -15617,8 +16865,12 @@
           <t>Barrancabermeja</t>
         </is>
       </c>
-      <c r="C914" t="inlineStr"/>
-      <c r="D914" t="inlineStr"/>
+      <c r="C914" t="n">
+        <v>7.067331</v>
+      </c>
+      <c r="D914" t="n">
+        <v>-73.852563</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -15631,8 +16883,12 @@
           <t>Betulia</t>
         </is>
       </c>
-      <c r="C915" t="inlineStr"/>
-      <c r="D915" t="inlineStr"/>
+      <c r="C915" t="n">
+        <v>6.90064</v>
+      </c>
+      <c r="D915" t="n">
+        <v>-73.283559</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -15645,8 +16901,12 @@
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="C916" t="inlineStr"/>
-      <c r="D916" t="inlineStr"/>
+      <c r="C916" t="n">
+        <v>5.98998</v>
+      </c>
+      <c r="D916" t="n">
+        <v>-73.77054800000001</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -15659,8 +16919,12 @@
           <t>Cabrera</t>
         </is>
       </c>
-      <c r="C917" t="inlineStr"/>
-      <c r="D917" t="inlineStr"/>
+      <c r="C917" t="n">
+        <v>6.593352</v>
+      </c>
+      <c r="D917" t="n">
+        <v>-73.246398</v>
+      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -15673,8 +16937,12 @@
           <t>Bucaramanga</t>
         </is>
       </c>
-      <c r="C918" t="inlineStr"/>
-      <c r="D918" t="inlineStr"/>
+      <c r="C918" t="n">
+        <v>7.127459</v>
+      </c>
+      <c r="D918" t="n">
+        <v>-73.11913</v>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -15687,8 +16955,12 @@
           <t>California</t>
         </is>
       </c>
-      <c r="C919" t="inlineStr"/>
-      <c r="D919" t="inlineStr"/>
+      <c r="C919" t="n">
+        <v>7.348091</v>
+      </c>
+      <c r="D919" t="n">
+        <v>-72.94592900000001</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -15701,8 +16973,12 @@
           <t>Capitanejo</t>
         </is>
       </c>
-      <c r="C920" t="inlineStr"/>
-      <c r="D920" t="inlineStr"/>
+      <c r="C920" t="n">
+        <v>6.52918</v>
+      </c>
+      <c r="D920" t="n">
+        <v>-72.698262</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -15715,8 +16991,12 @@
           <t>Carcasí</t>
         </is>
       </c>
-      <c r="C921" t="inlineStr"/>
-      <c r="D921" t="inlineStr"/>
+      <c r="C921" t="n">
+        <v>6.627352</v>
+      </c>
+      <c r="D921" t="n">
+        <v>-72.626097</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -15729,8 +17009,12 @@
           <t>Cepitá</t>
         </is>
       </c>
-      <c r="C922" t="inlineStr"/>
-      <c r="D922" t="inlineStr"/>
+      <c r="C922" t="n">
+        <v>6.745901</v>
+      </c>
+      <c r="D922" t="n">
+        <v>-72.929429</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -15743,8 +17027,12 @@
           <t>Cerrito</t>
         </is>
       </c>
-      <c r="C923" t="inlineStr"/>
-      <c r="D923" t="inlineStr"/>
+      <c r="C923" t="n">
+        <v>6.843599</v>
+      </c>
+      <c r="D923" t="n">
+        <v>-72.693963</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -15757,8 +17045,12 @@
           <t>Charalá</t>
         </is>
       </c>
-      <c r="C924" t="inlineStr"/>
-      <c r="D924" t="inlineStr"/>
+      <c r="C924" t="n">
+        <v>6.288174</v>
+      </c>
+      <c r="D924" t="n">
+        <v>-73.14828900000001</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -15771,8 +17063,12 @@
           <t>Charta</t>
         </is>
       </c>
-      <c r="C925" t="inlineStr"/>
-      <c r="D925" t="inlineStr"/>
+      <c r="C925" t="n">
+        <v>7.280799</v>
+      </c>
+      <c r="D925" t="n">
+        <v>-72.968226</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -15785,8 +17081,12 @@
           <t>Chima</t>
         </is>
       </c>
-      <c r="C926" t="inlineStr"/>
-      <c r="D926" t="inlineStr"/>
+      <c r="C926" t="n">
+        <v>6.344397</v>
+      </c>
+      <c r="D926" t="n">
+        <v>-73.372743</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -15799,8 +17099,12 @@
           <t>Chipatá</t>
         </is>
       </c>
-      <c r="C927" t="inlineStr"/>
-      <c r="D927" t="inlineStr"/>
+      <c r="C927" t="n">
+        <v>6.062477</v>
+      </c>
+      <c r="D927" t="n">
+        <v>-73.637253</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -15813,8 +17117,12 @@
           <t>Cimitarra</t>
         </is>
       </c>
-      <c r="C928" t="inlineStr"/>
-      <c r="D928" t="inlineStr"/>
+      <c r="C928" t="n">
+        <v>6.314541</v>
+      </c>
+      <c r="D928" t="n">
+        <v>-73.949681</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -15827,8 +17135,12 @@
           <t>Concepción</t>
         </is>
       </c>
-      <c r="C929" t="inlineStr"/>
-      <c r="D929" t="inlineStr"/>
+      <c r="C929" t="n">
+        <v>6.768293</v>
+      </c>
+      <c r="D929" t="n">
+        <v>-72.694484</v>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -15841,8 +17153,12 @@
           <t>Confines</t>
         </is>
       </c>
-      <c r="C930" t="inlineStr"/>
-      <c r="D930" t="inlineStr"/>
+      <c r="C930" t="n">
+        <v>6.355975</v>
+      </c>
+      <c r="D930" t="n">
+        <v>-73.24096299999999</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -15855,8 +17171,12 @@
           <t>Contratación</t>
         </is>
       </c>
-      <c r="C931" t="inlineStr"/>
-      <c r="D931" t="inlineStr"/>
+      <c r="C931" t="n">
+        <v>6.290737</v>
+      </c>
+      <c r="D931" t="n">
+        <v>-73.47455600000001</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -15869,8 +17189,12 @@
           <t>Coromoro</t>
         </is>
       </c>
-      <c r="C932" t="inlineStr"/>
-      <c r="D932" t="inlineStr"/>
+      <c r="C932" t="n">
+        <v>6.240506</v>
+      </c>
+      <c r="D932" t="n">
+        <v>-72.991731</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -15883,8 +17207,12 @@
           <t>Curití</t>
         </is>
       </c>
-      <c r="C933" t="inlineStr"/>
-      <c r="D933" t="inlineStr"/>
+      <c r="C933" t="n">
+        <v>6.606703</v>
+      </c>
+      <c r="D933" t="n">
+        <v>-73.069209</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -15897,8 +17225,12 @@
           <t>El Carmen de Chucurí</t>
         </is>
       </c>
-      <c r="C934" t="inlineStr"/>
-      <c r="D934" t="inlineStr"/>
+      <c r="C934" t="n">
+        <v>6.698692</v>
+      </c>
+      <c r="D934" t="n">
+        <v>-73.51156899999999</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -15911,8 +17243,12 @@
           <t>El Guacamayo</t>
         </is>
       </c>
-      <c r="C935" t="inlineStr"/>
-      <c r="D935" t="inlineStr"/>
+      <c r="C935" t="n">
+        <v>6.245266</v>
+      </c>
+      <c r="D935" t="n">
+        <v>-73.497561</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -15925,8 +17261,12 @@
           <t>El Peñón</t>
         </is>
       </c>
-      <c r="C936" t="inlineStr"/>
-      <c r="D936" t="inlineStr"/>
+      <c r="C936" t="n">
+        <v>6.055759</v>
+      </c>
+      <c r="D936" t="n">
+        <v>-73.814993</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -15939,8 +17279,12 @@
           <t>El Playón</t>
         </is>
       </c>
-      <c r="C937" t="inlineStr"/>
-      <c r="D937" t="inlineStr"/>
+      <c r="C937" t="n">
+        <v>7.470211</v>
+      </c>
+      <c r="D937" t="n">
+        <v>-73.202603</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -15953,8 +17297,12 @@
           <t>Encino</t>
         </is>
       </c>
-      <c r="C938" t="inlineStr"/>
-      <c r="D938" t="inlineStr"/>
+      <c r="C938" t="n">
+        <v>6.137825</v>
+      </c>
+      <c r="D938" t="n">
+        <v>-73.098837</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -15967,8 +17315,12 @@
           <t>Enciso</t>
         </is>
       </c>
-      <c r="C939" t="inlineStr"/>
-      <c r="D939" t="inlineStr"/>
+      <c r="C939" t="n">
+        <v>6.649845</v>
+      </c>
+      <c r="D939" t="n">
+        <v>-72.681736</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -15981,8 +17333,12 @@
           <t>Florián</t>
         </is>
       </c>
-      <c r="C940" t="inlineStr"/>
-      <c r="D940" t="inlineStr"/>
+      <c r="C940" t="n">
+        <v>5.802419</v>
+      </c>
+      <c r="D940" t="n">
+        <v>-73.970934</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -15995,8 +17351,12 @@
           <t>Floridablanca</t>
         </is>
       </c>
-      <c r="C941" t="inlineStr"/>
-      <c r="D941" t="inlineStr"/>
+      <c r="C941" t="n">
+        <v>7.062568</v>
+      </c>
+      <c r="D941" t="n">
+        <v>-73.085909</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -16009,8 +17369,12 @@
           <t>Galán</t>
         </is>
       </c>
-      <c r="C942" t="inlineStr"/>
-      <c r="D942" t="inlineStr"/>
+      <c r="C942" t="n">
+        <v>6.63791</v>
+      </c>
+      <c r="D942" t="n">
+        <v>-73.287453</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -16023,8 +17387,12 @@
           <t>Gámbita</t>
         </is>
       </c>
-      <c r="C943" t="inlineStr"/>
-      <c r="D943" t="inlineStr"/>
+      <c r="C943" t="n">
+        <v>5.91628</v>
+      </c>
+      <c r="D943" t="n">
+        <v>-73.31589700000001</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -16037,8 +17405,12 @@
           <t>Girón</t>
         </is>
       </c>
-      <c r="C944" t="inlineStr"/>
-      <c r="D944" t="inlineStr"/>
+      <c r="C944" t="n">
+        <v>7.069069</v>
+      </c>
+      <c r="D944" t="n">
+        <v>-73.170028</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -16051,8 +17423,12 @@
           <t>Guaca</t>
         </is>
       </c>
-      <c r="C945" t="inlineStr"/>
-      <c r="D945" t="inlineStr"/>
+      <c r="C945" t="n">
+        <v>6.876076</v>
+      </c>
+      <c r="D945" t="n">
+        <v>-72.85576399999999</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -16065,8 +17441,12 @@
           <t>Guadalupe</t>
         </is>
       </c>
-      <c r="C946" t="inlineStr"/>
-      <c r="D946" t="inlineStr"/>
+      <c r="C946" t="n">
+        <v>6.246817</v>
+      </c>
+      <c r="D946" t="n">
+        <v>-73.418182</v>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -16079,8 +17459,12 @@
           <t>Guapotá</t>
         </is>
       </c>
-      <c r="C947" t="inlineStr"/>
-      <c r="D947" t="inlineStr"/>
+      <c r="C947" t="n">
+        <v>6.308298</v>
+      </c>
+      <c r="D947" t="n">
+        <v>-73.321224</v>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -16093,8 +17477,12 @@
           <t>Guavatá</t>
         </is>
       </c>
-      <c r="C948" t="inlineStr"/>
-      <c r="D948" t="inlineStr"/>
+      <c r="C948" t="n">
+        <v>5.954265</v>
+      </c>
+      <c r="D948" t="n">
+        <v>-73.699788</v>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -16107,8 +17495,12 @@
           <t>Güepsa</t>
         </is>
       </c>
-      <c r="C949" t="inlineStr"/>
-      <c r="D949" t="inlineStr"/>
+      <c r="C949" t="n">
+        <v>6.035726</v>
+      </c>
+      <c r="D949" t="n">
+        <v>-73.56632399999999</v>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -16121,8 +17513,12 @@
           <t>Hato</t>
         </is>
       </c>
-      <c r="C950" t="inlineStr"/>
-      <c r="D950" t="inlineStr"/>
+      <c r="C950" t="n">
+        <v>6.562107</v>
+      </c>
+      <c r="D950" t="n">
+        <v>-73.364738</v>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -16135,8 +17531,12 @@
           <t>Jesús María</t>
         </is>
       </c>
-      <c r="C951" t="inlineStr"/>
-      <c r="D951" t="inlineStr"/>
+      <c r="C951" t="n">
+        <v>5.848979</v>
+      </c>
+      <c r="D951" t="n">
+        <v>-73.83109899999999</v>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -16149,8 +17549,12 @@
           <t>Jordán</t>
         </is>
       </c>
-      <c r="C952" t="inlineStr"/>
-      <c r="D952" t="inlineStr"/>
+      <c r="C952" t="n">
+        <v>6.712707</v>
+      </c>
+      <c r="D952" t="n">
+        <v>-73.092454</v>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -16163,8 +17567,12 @@
           <t>La Belleza</t>
         </is>
       </c>
-      <c r="C953" t="inlineStr"/>
-      <c r="D953" t="inlineStr"/>
+      <c r="C953" t="n">
+        <v>5.8588396</v>
+      </c>
+      <c r="D953" t="n">
+        <v>-73.96582909999999</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -16177,8 +17585,12 @@
           <t>La Paz</t>
         </is>
       </c>
-      <c r="C954" t="inlineStr"/>
-      <c r="D954" t="inlineStr"/>
+      <c r="C954" t="n">
+        <v>6.178593</v>
+      </c>
+      <c r="D954" t="n">
+        <v>-73.589584</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -16191,8 +17603,12 @@
           <t>Landázuri</t>
         </is>
       </c>
-      <c r="C955" t="inlineStr"/>
-      <c r="D955" t="inlineStr"/>
+      <c r="C955" t="n">
+        <v>6.220533</v>
+      </c>
+      <c r="D955" t="n">
+        <v>-73.811375</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -16205,8 +17621,12 @@
           <t>Lebrija</t>
         </is>
       </c>
-      <c r="C956" t="inlineStr"/>
-      <c r="D956" t="inlineStr"/>
+      <c r="C956" t="n">
+        <v>7.113842</v>
+      </c>
+      <c r="D956" t="n">
+        <v>-73.217406</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -16219,8 +17639,12 @@
           <t>Los Santos</t>
         </is>
       </c>
-      <c r="C957" t="inlineStr"/>
-      <c r="D957" t="inlineStr"/>
+      <c r="C957" t="n">
+        <v>6.817872</v>
+      </c>
+      <c r="D957" t="n">
+        <v>-73.096114</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -16233,8 +17657,12 @@
           <t>Macaravita</t>
         </is>
       </c>
-      <c r="C958" t="inlineStr"/>
-      <c r="D958" t="inlineStr"/>
+      <c r="C958" t="n">
+        <v>6.506171</v>
+      </c>
+      <c r="D958" t="n">
+        <v>-72.592896</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -16247,8 +17675,12 @@
           <t>Málaga</t>
         </is>
       </c>
-      <c r="C959" t="inlineStr"/>
-      <c r="D959" t="inlineStr"/>
+      <c r="C959" t="n">
+        <v>6.699661</v>
+      </c>
+      <c r="D959" t="n">
+        <v>-72.732456</v>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -16261,8 +17693,12 @@
           <t>Matanza</t>
         </is>
       </c>
-      <c r="C960" t="inlineStr"/>
-      <c r="D960" t="inlineStr"/>
+      <c r="C960" t="n">
+        <v>7.323081</v>
+      </c>
+      <c r="D960" t="n">
+        <v>-73.015568</v>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -16275,8 +17711,12 @@
           <t>Mogotes</t>
         </is>
       </c>
-      <c r="C961" t="inlineStr"/>
-      <c r="D961" t="inlineStr"/>
+      <c r="C961" t="n">
+        <v>6.502441</v>
+      </c>
+      <c r="D961" t="n">
+        <v>-72.976792</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -16289,8 +17729,12 @@
           <t>Molagavita</t>
         </is>
       </c>
-      <c r="C962" t="inlineStr"/>
-      <c r="D962" t="inlineStr"/>
+      <c r="C962" t="n">
+        <v>6.673729</v>
+      </c>
+      <c r="D962" t="n">
+        <v>-72.80911399999999</v>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -16303,8 +17747,12 @@
           <t>Ocamonte</t>
         </is>
       </c>
-      <c r="C963" t="inlineStr"/>
-      <c r="D963" t="inlineStr"/>
+      <c r="C963" t="n">
+        <v>6.34072</v>
+      </c>
+      <c r="D963" t="n">
+        <v>-73.12202600000001</v>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -16317,8 +17765,12 @@
           <t>Oiba</t>
         </is>
       </c>
-      <c r="C964" t="inlineStr"/>
-      <c r="D964" t="inlineStr"/>
+      <c r="C964" t="n">
+        <v>6.2642</v>
+      </c>
+      <c r="D964" t="n">
+        <v>-73.29877999999999</v>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -16331,8 +17783,12 @@
           <t>Onzaga</t>
         </is>
       </c>
-      <c r="C965" t="inlineStr"/>
-      <c r="D965" t="inlineStr"/>
+      <c r="C965" t="n">
+        <v>6.343897</v>
+      </c>
+      <c r="D965" t="n">
+        <v>-72.81660599999999</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -16345,8 +17801,12 @@
           <t>Palmar</t>
         </is>
       </c>
-      <c r="C966" t="inlineStr"/>
-      <c r="D966" t="inlineStr"/>
+      <c r="C966" t="n">
+        <v>6.538635</v>
+      </c>
+      <c r="D966" t="n">
+        <v>-73.291693</v>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -16359,8 +17819,12 @@
           <t>Palmas del Socorro</t>
         </is>
       </c>
-      <c r="C967" t="inlineStr"/>
-      <c r="D967" t="inlineStr"/>
+      <c r="C967" t="n">
+        <v>6.406625</v>
+      </c>
+      <c r="D967" t="n">
+        <v>-73.287918</v>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -16373,8 +17837,12 @@
           <t>Páramo</t>
         </is>
       </c>
-      <c r="C968" t="inlineStr"/>
-      <c r="D968" t="inlineStr"/>
+      <c r="C968" t="n">
+        <v>6.416541</v>
+      </c>
+      <c r="D968" t="n">
+        <v>-73.169399</v>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -16387,8 +17855,12 @@
           <t>Piedecuesta</t>
         </is>
       </c>
-      <c r="C969" t="inlineStr"/>
-      <c r="D969" t="inlineStr"/>
+      <c r="C969" t="n">
+        <v>6.987481</v>
+      </c>
+      <c r="D969" t="n">
+        <v>-73.05041300000001</v>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -16401,8 +17873,12 @@
           <t>Pinchote</t>
         </is>
       </c>
-      <c r="C970" t="inlineStr"/>
-      <c r="D970" t="inlineStr"/>
+      <c r="C970" t="n">
+        <v>6.53225</v>
+      </c>
+      <c r="D970" t="n">
+        <v>-73.17323</v>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -16415,8 +17891,12 @@
           <t>Puente Nacional</t>
         </is>
       </c>
-      <c r="C971" t="inlineStr"/>
-      <c r="D971" t="inlineStr"/>
+      <c r="C971" t="n">
+        <v>5.877096</v>
+      </c>
+      <c r="D971" t="n">
+        <v>-73.679106</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -16429,8 +17909,12 @@
           <t>Puerto Parra</t>
         </is>
       </c>
-      <c r="C972" t="inlineStr"/>
-      <c r="D972" t="inlineStr"/>
+      <c r="C972" t="n">
+        <v>6.701289</v>
+      </c>
+      <c r="D972" t="n">
+        <v>-73.977478</v>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -16443,8 +17927,12 @@
           <t>Puerto Wilches</t>
         </is>
       </c>
-      <c r="C973" t="inlineStr"/>
-      <c r="D973" t="inlineStr"/>
+      <c r="C973" t="n">
+        <v>7.348018</v>
+      </c>
+      <c r="D973" t="n">
+        <v>-73.89797799999999</v>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -16457,8 +17945,12 @@
           <t>Rionegro</t>
         </is>
       </c>
-      <c r="C974" t="inlineStr"/>
-      <c r="D974" t="inlineStr"/>
+      <c r="C974" t="n">
+        <v>7.479289</v>
+      </c>
+      <c r="D974" t="n">
+        <v>-73.382701</v>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -16471,8 +17963,12 @@
           <t>Sabana de Torres</t>
         </is>
       </c>
-      <c r="C975" t="inlineStr"/>
-      <c r="D975" t="inlineStr"/>
+      <c r="C975" t="n">
+        <v>7.393942</v>
+      </c>
+      <c r="D975" t="n">
+        <v>-73.499886</v>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -16485,8 +17981,12 @@
           <t>San Andrés</t>
         </is>
       </c>
-      <c r="C976" t="inlineStr"/>
-      <c r="D976" t="inlineStr"/>
+      <c r="C976" t="n">
+        <v>6.810067</v>
+      </c>
+      <c r="D976" t="n">
+        <v>-72.850635</v>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -16499,8 +17999,12 @@
           <t>San Benito</t>
         </is>
       </c>
-      <c r="C977" t="inlineStr"/>
-      <c r="D977" t="inlineStr"/>
+      <c r="C977" t="n">
+        <v>6.103226</v>
+      </c>
+      <c r="D977" t="n">
+        <v>-73.53013900000001</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -16513,8 +18017,12 @@
           <t>San Gil</t>
         </is>
       </c>
-      <c r="C978" t="inlineStr"/>
-      <c r="D978" t="inlineStr"/>
+      <c r="C978" t="n">
+        <v>6.555286</v>
+      </c>
+      <c r="D978" t="n">
+        <v>-73.131235</v>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -16527,8 +18035,12 @@
           <t>San Joaquín</t>
         </is>
       </c>
-      <c r="C979" t="inlineStr"/>
-      <c r="D979" t="inlineStr"/>
+      <c r="C979" t="n">
+        <v>6.427589</v>
+      </c>
+      <c r="D979" t="n">
+        <v>-72.867653</v>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -16541,8 +18053,12 @@
           <t>San José de Miranda</t>
         </is>
       </c>
-      <c r="C980" t="inlineStr"/>
-      <c r="D980" t="inlineStr"/>
+      <c r="C980" t="n">
+        <v>6.658387</v>
+      </c>
+      <c r="D980" t="n">
+        <v>-72.73348900000001</v>
+      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -16555,8 +18071,12 @@
           <t>San Miguel</t>
         </is>
       </c>
-      <c r="C981" t="inlineStr"/>
-      <c r="D981" t="inlineStr"/>
+      <c r="C981" t="n">
+        <v>6.575929</v>
+      </c>
+      <c r="D981" t="n">
+        <v>-72.645549</v>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -16569,8 +18089,12 @@
           <t>San Vicente de Chucurí</t>
         </is>
       </c>
-      <c r="C982" t="inlineStr"/>
-      <c r="D982" t="inlineStr"/>
+      <c r="C982" t="n">
+        <v>6.928779</v>
+      </c>
+      <c r="D982" t="n">
+        <v>-73.520754</v>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -16583,8 +18107,12 @@
           <t>Santa Bárbara</t>
         </is>
       </c>
-      <c r="C983" t="inlineStr"/>
-      <c r="D983" t="inlineStr"/>
+      <c r="C983" t="n">
+        <v>6.963224</v>
+      </c>
+      <c r="D983" t="n">
+        <v>-72.905564</v>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
@@ -16597,8 +18125,12 @@
           <t>Santa Helena del Opón</t>
         </is>
       </c>
-      <c r="C984" t="inlineStr"/>
-      <c r="D984" t="inlineStr"/>
+      <c r="C984" t="n">
+        <v>6.338798</v>
+      </c>
+      <c r="D984" t="n">
+        <v>-73.616366</v>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -16611,8 +18143,12 @@
           <t>Simacota</t>
         </is>
       </c>
-      <c r="C985" t="inlineStr"/>
-      <c r="D985" t="inlineStr"/>
+      <c r="C985" t="n">
+        <v>6.68248</v>
+      </c>
+      <c r="D985" t="n">
+        <v>-73.791692</v>
+      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -16625,8 +18161,12 @@
           <t>Socorro</t>
         </is>
       </c>
-      <c r="C986" t="inlineStr"/>
-      <c r="D986" t="inlineStr"/>
+      <c r="C986" t="n">
+        <v>6.470518</v>
+      </c>
+      <c r="D986" t="n">
+        <v>-73.26231900000001</v>
+      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -16639,8 +18179,12 @@
           <t>Suaita</t>
         </is>
       </c>
-      <c r="C987" t="inlineStr"/>
-      <c r="D987" t="inlineStr"/>
+      <c r="C987" t="n">
+        <v>6.125754</v>
+      </c>
+      <c r="D987" t="n">
+        <v>-73.36271499999999</v>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -16653,8 +18197,12 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="C988" t="inlineStr"/>
-      <c r="D988" t="inlineStr"/>
+      <c r="C988" t="n">
+        <v>6.015965</v>
+      </c>
+      <c r="D988" t="n">
+        <v>-74.01211000000001</v>
+      </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
@@ -16667,8 +18215,12 @@
           <t>Suratá</t>
         </is>
       </c>
-      <c r="C989" t="inlineStr"/>
-      <c r="D989" t="inlineStr"/>
+      <c r="C989" t="n">
+        <v>7.366493</v>
+      </c>
+      <c r="D989" t="n">
+        <v>-72.984736</v>
+      </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
@@ -16681,8 +18233,12 @@
           <t>Tona</t>
         </is>
       </c>
-      <c r="C990" t="inlineStr"/>
-      <c r="D990" t="inlineStr"/>
+      <c r="C990" t="n">
+        <v>7.202063</v>
+      </c>
+      <c r="D990" t="n">
+        <v>-72.966373</v>
+      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -16695,8 +18251,12 @@
           <t>Valle de San José</t>
         </is>
       </c>
-      <c r="C991" t="inlineStr"/>
-      <c r="D991" t="inlineStr"/>
+      <c r="C991" t="n">
+        <v>6.448015</v>
+      </c>
+      <c r="D991" t="n">
+        <v>-73.144301</v>
+      </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
@@ -16709,8 +18269,12 @@
           <t>Vélez</t>
         </is>
       </c>
-      <c r="C992" t="inlineStr"/>
-      <c r="D992" t="inlineStr"/>
+      <c r="C992" t="n">
+        <v>6.012363</v>
+      </c>
+      <c r="D992" t="n">
+        <v>-73.67296</v>
+      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -16723,8 +18287,12 @@
           <t>Vetas</t>
         </is>
       </c>
-      <c r="C993" t="inlineStr"/>
-      <c r="D993" t="inlineStr"/>
+      <c r="C993" t="n">
+        <v>7.309264</v>
+      </c>
+      <c r="D993" t="n">
+        <v>-72.871808</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
@@ -16737,8 +18305,12 @@
           <t>Villanueva</t>
         </is>
       </c>
-      <c r="C994" t="inlineStr"/>
-      <c r="D994" t="inlineStr"/>
+      <c r="C994" t="n">
+        <v>6.671239</v>
+      </c>
+      <c r="D994" t="n">
+        <v>-73.175398</v>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -16751,8 +18323,12 @@
           <t>Zapatoca</t>
         </is>
       </c>
-      <c r="C995" t="inlineStr"/>
-      <c r="D995" t="inlineStr"/>
+      <c r="C995" t="n">
+        <v>6.8166596</v>
+      </c>
+      <c r="D995" t="n">
+        <v>-73.26865290000001</v>
+      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -16765,8 +18341,12 @@
           <t>Buenavista</t>
         </is>
       </c>
-      <c r="C996" t="inlineStr"/>
-      <c r="D996" t="inlineStr"/>
+      <c r="C996" t="n">
+        <v>9.319618999999999</v>
+      </c>
+      <c r="D996" t="n">
+        <v>-74.974587</v>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
@@ -16779,8 +18359,12 @@
           <t>Caimito</t>
         </is>
       </c>
-      <c r="C997" t="inlineStr"/>
-      <c r="D997" t="inlineStr"/>
+      <c r="C997" t="n">
+        <v>8.790590999999999</v>
+      </c>
+      <c r="D997" t="n">
+        <v>-75.11631800000001</v>
+      </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
@@ -16793,8 +18377,12 @@
           <t>Chalán</t>
         </is>
       </c>
-      <c r="C998" t="inlineStr"/>
-      <c r="D998" t="inlineStr"/>
+      <c r="C998" t="n">
+        <v>9.542396999999999</v>
+      </c>
+      <c r="D998" t="n">
+        <v>-75.31294699999999</v>
+      </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
@@ -16807,8 +18395,12 @@
           <t>Colosó</t>
         </is>
       </c>
-      <c r="C999" t="inlineStr"/>
-      <c r="D999" t="inlineStr"/>
+      <c r="C999" t="n">
+        <v>9.494108000000001</v>
+      </c>
+      <c r="D999" t="n">
+        <v>-75.353087</v>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -16821,8 +18413,12 @@
           <t>Corozal</t>
         </is>
       </c>
-      <c r="C1000" t="inlineStr"/>
-      <c r="D1000" t="inlineStr"/>
+      <c r="C1000" t="n">
+        <v>9.319239</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>-75.294726</v>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
@@ -16835,8 +18431,12 @@
           <t>Coveñas</t>
         </is>
       </c>
-      <c r="C1001" t="inlineStr"/>
-      <c r="D1001" t="inlineStr"/>
+      <c r="C1001" t="n">
+        <v>9.401757999999999</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>-75.678702</v>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
@@ -16849,8 +18449,12 @@
           <t>El Roble</t>
         </is>
       </c>
-      <c r="C1002" t="inlineStr"/>
-      <c r="D1002" t="inlineStr"/>
+      <c r="C1002" t="n">
+        <v>9.103770000000001</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>-75.195262</v>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -16863,8 +18467,12 @@
           <t>Galeras</t>
         </is>
       </c>
-      <c r="C1003" t="inlineStr"/>
-      <c r="D1003" t="inlineStr"/>
+      <c r="C1003" t="n">
+        <v>9.120965999999999</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>-74.966027</v>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -16877,8 +18485,12 @@
           <t>Guaranda</t>
         </is>
       </c>
-      <c r="C1004" t="inlineStr"/>
-      <c r="D1004" t="inlineStr"/>
+      <c r="C1004" t="n">
+        <v>8.392953</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>-74.800117</v>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -16891,8 +18503,12 @@
           <t>Sincelejo</t>
         </is>
       </c>
-      <c r="C1005" t="inlineStr"/>
-      <c r="D1005" t="inlineStr"/>
+      <c r="C1005" t="n">
+        <v>9.297338999999999</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>-75.39266000000001</v>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -16905,8 +18521,12 @@
           <t>La Unión</t>
         </is>
       </c>
-      <c r="C1006" t="inlineStr"/>
-      <c r="D1006" t="inlineStr"/>
+      <c r="C1006" t="n">
+        <v>8.851812000000001</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>-75.28046500000001</v>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
@@ -16919,8 +18539,12 @@
           <t>Los Palmitos</t>
         </is>
       </c>
-      <c r="C1007" t="inlineStr"/>
-      <c r="D1007" t="inlineStr"/>
+      <c r="C1007" t="n">
+        <v>9.380553000000001</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>-75.26813300000001</v>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -16933,8 +18557,12 @@
           <t>Majagual</t>
         </is>
       </c>
-      <c r="C1008" t="inlineStr"/>
-      <c r="D1008" t="inlineStr"/>
+      <c r="C1008" t="n">
+        <v>8.561871</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>-74.729446</v>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
@@ -16947,8 +18575,12 @@
           <t>Morroa</t>
         </is>
       </c>
-      <c r="C1009" t="inlineStr"/>
-      <c r="D1009" t="inlineStr"/>
+      <c r="C1009" t="n">
+        <v>9.33441</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>-75.305435</v>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
@@ -16961,8 +18593,12 @@
           <t>Ovejas</t>
         </is>
       </c>
-      <c r="C1010" t="inlineStr"/>
-      <c r="D1010" t="inlineStr"/>
+      <c r="C1010" t="n">
+        <v>9.553839999999999</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>-75.18883099999999</v>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
@@ -16975,8 +18611,12 @@
           <t>Palmito</t>
         </is>
       </c>
-      <c r="C1011" t="inlineStr"/>
-      <c r="D1011" t="inlineStr"/>
+      <c r="C1011" t="n">
+        <v>9.331825</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>-75.542288</v>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -16989,8 +18629,12 @@
           <t>Sampués</t>
         </is>
       </c>
-      <c r="C1012" t="inlineStr"/>
-      <c r="D1012" t="inlineStr"/>
+      <c r="C1012" t="n">
+        <v>9.184558000000001</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>-75.38023699999999</v>
+      </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
@@ -17003,8 +18647,12 @@
           <t>San Benito Abad</t>
         </is>
       </c>
-      <c r="C1013" t="inlineStr"/>
-      <c r="D1013" t="inlineStr"/>
+      <c r="C1013" t="n">
+        <v>8.929356</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>-75.02691</v>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -17017,8 +18665,12 @@
           <t>San Juan de Betulia</t>
         </is>
       </c>
-      <c r="C1014" t="inlineStr"/>
-      <c r="D1014" t="inlineStr"/>
+      <c r="C1014" t="n">
+        <v>9.273498999999999</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>-75.243118</v>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -17031,8 +18683,12 @@
           <t>San Marcos</t>
         </is>
       </c>
-      <c r="C1015" t="inlineStr"/>
-      <c r="D1015" t="inlineStr"/>
+      <c r="C1015" t="n">
+        <v>8.661861</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>-75.130764</v>
+      </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -17045,8 +18701,12 @@
           <t>San Onofre</t>
         </is>
       </c>
-      <c r="C1016" t="inlineStr"/>
-      <c r="D1016" t="inlineStr"/>
+      <c r="C1016" t="n">
+        <v>9.738626</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>-75.52342299999999</v>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -17059,8 +18719,12 @@
           <t>San Pedro</t>
         </is>
       </c>
-      <c r="C1017" t="inlineStr"/>
-      <c r="D1017" t="inlineStr"/>
+      <c r="C1017" t="n">
+        <v>9.39663</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>-75.033546</v>
+      </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
@@ -17073,8 +18737,12 @@
           <t>Santiago de Tolú</t>
         </is>
       </c>
-      <c r="C1018" t="inlineStr"/>
-      <c r="D1018" t="inlineStr"/>
+      <c r="C1018" t="n">
+        <v>9.524114000000001</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>-75.58417900000001</v>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -17087,8 +18755,12 @@
           <t>Sincé</t>
         </is>
       </c>
-      <c r="C1019" t="inlineStr"/>
-      <c r="D1019" t="inlineStr"/>
+      <c r="C1019" t="n">
+        <v>9.244011</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>-75.14740399999999</v>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
@@ -17101,8 +18773,12 @@
           <t>Sucre</t>
         </is>
       </c>
-      <c r="C1020" t="inlineStr"/>
-      <c r="D1020" t="inlineStr"/>
+      <c r="C1020" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
@@ -17115,8 +18791,12 @@
           <t>Tolúviejo</t>
         </is>
       </c>
-      <c r="C1021" t="inlineStr"/>
-      <c r="D1021" t="inlineStr"/>
+      <c r="C1021" t="n">
+        <v>9.453506000000001</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>-75.43929900000001</v>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
@@ -17129,8 +18809,12 @@
           <t>Alpujarra</t>
         </is>
       </c>
-      <c r="C1022" t="inlineStr"/>
-      <c r="D1022" t="inlineStr"/>
+      <c r="C1022" t="n">
+        <v>3.391033</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>-74.93260100000001</v>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -17143,8 +18827,12 @@
           <t>Alvarado</t>
         </is>
       </c>
-      <c r="C1023" t="inlineStr"/>
-      <c r="D1023" t="inlineStr"/>
+      <c r="C1023" t="n">
+        <v>4.567169</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>-74.95382499999999</v>
+      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -17157,8 +18845,12 @@
           <t>Ambalema</t>
         </is>
       </c>
-      <c r="C1024" t="inlineStr"/>
-      <c r="D1024" t="inlineStr"/>
+      <c r="C1024" t="n">
+        <v>4.783587</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>-74.764393</v>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -17171,8 +18863,12 @@
           <t>Anzoátegui</t>
         </is>
       </c>
-      <c r="C1025" t="inlineStr"/>
-      <c r="D1025" t="inlineStr"/>
+      <c r="C1025" t="n">
+        <v>4.657884</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>-75.328035</v>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -17185,8 +18881,12 @@
           <t>Armero</t>
         </is>
       </c>
-      <c r="C1026" t="inlineStr"/>
-      <c r="D1026" t="inlineStr"/>
+      <c r="C1026" t="n">
+        <v>4.962324</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>-74.905903</v>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -17199,8 +18899,12 @@
           <t>Ataco</t>
         </is>
       </c>
-      <c r="C1027" t="inlineStr"/>
-      <c r="D1027" t="inlineStr"/>
+      <c r="C1027" t="n">
+        <v>3.591217</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>-75.381946</v>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
@@ -17213,8 +18917,12 @@
           <t>Cajamarca</t>
         </is>
       </c>
-      <c r="C1028" t="inlineStr"/>
-      <c r="D1028" t="inlineStr"/>
+      <c r="C1028" t="n">
+        <v>4.441966</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>-75.426821</v>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
@@ -17227,8 +18935,12 @@
           <t>Carmen de Apicalá</t>
         </is>
       </c>
-      <c r="C1029" t="inlineStr"/>
-      <c r="D1029" t="inlineStr"/>
+      <c r="C1029" t="n">
+        <v>4.147832</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>-74.722442</v>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -17241,8 +18953,12 @@
           <t>Casabianca</t>
         </is>
       </c>
-      <c r="C1030" t="inlineStr"/>
-      <c r="D1030" t="inlineStr"/>
+      <c r="C1030" t="n">
+        <v>5.004677</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>-75.19489299999999</v>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -17255,8 +18971,12 @@
           <t>Ibagué</t>
         </is>
       </c>
-      <c r="C1031" t="inlineStr"/>
-      <c r="D1031" t="inlineStr"/>
+      <c r="C1031" t="n">
+        <v>4.438603</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>-75.210886</v>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -17269,8 +18989,12 @@
           <t>Chaparral</t>
         </is>
       </c>
-      <c r="C1032" t="inlineStr"/>
-      <c r="D1032" t="inlineStr"/>
+      <c r="C1032" t="n">
+        <v>3.724585</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>-75.485156</v>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -17283,8 +19007,12 @@
           <t>Coello</t>
         </is>
       </c>
-      <c r="C1033" t="inlineStr"/>
-      <c r="D1033" t="inlineStr"/>
+      <c r="C1033" t="n">
+        <v>4.288072</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>-74.898169</v>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -17297,8 +19025,12 @@
           <t>Coyaima</t>
         </is>
       </c>
-      <c r="C1034" t="inlineStr"/>
-      <c r="D1034" t="inlineStr"/>
+      <c r="C1034" t="n">
+        <v>3.799391</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>-75.194586</v>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
@@ -17311,8 +19043,12 @@
           <t>Cunday</t>
         </is>
       </c>
-      <c r="C1035" t="inlineStr"/>
-      <c r="D1035" t="inlineStr"/>
+      <c r="C1035" t="n">
+        <v>3.965943</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>-74.726761</v>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -17325,8 +19061,12 @@
           <t>Dolores</t>
         </is>
       </c>
-      <c r="C1036" t="inlineStr"/>
-      <c r="D1036" t="inlineStr"/>
+      <c r="C1036" t="n">
+        <v>3.627568</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>-74.80978500000001</v>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -17339,8 +19079,12 @@
           <t>Espinal</t>
         </is>
       </c>
-      <c r="C1037" t="inlineStr"/>
-      <c r="D1037" t="inlineStr"/>
+      <c r="C1037" t="n">
+        <v>4.150304</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>-74.88459</v>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
@@ -17353,8 +19097,12 @@
           <t>Falan</t>
         </is>
       </c>
-      <c r="C1038" t="inlineStr"/>
-      <c r="D1038" t="inlineStr"/>
+      <c r="C1038" t="n">
+        <v>5.124023</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>-74.951618</v>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
@@ -17367,8 +19115,12 @@
           <t>Flandes</t>
         </is>
       </c>
-      <c r="C1039" t="inlineStr"/>
-      <c r="D1039" t="inlineStr"/>
+      <c r="C1039" t="n">
+        <v>4.2865</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>-74.813697</v>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -17381,8 +19133,12 @@
           <t>Fresno</t>
         </is>
       </c>
-      <c r="C1040" t="inlineStr"/>
-      <c r="D1040" t="inlineStr"/>
+      <c r="C1040" t="n">
+        <v>5.151659</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>-75.036635</v>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -17395,8 +19151,12 @@
           <t>Guamo</t>
         </is>
       </c>
-      <c r="C1041" t="inlineStr"/>
-      <c r="D1041" t="inlineStr"/>
+      <c r="C1041" t="n">
+        <v>4.030391</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>-74.967901</v>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
@@ -17409,8 +19169,12 @@
           <t>Herveo</t>
         </is>
       </c>
-      <c r="C1042" t="inlineStr"/>
-      <c r="D1042" t="inlineStr"/>
+      <c r="C1042" t="n">
+        <v>5.080104</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>-75.176211</v>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -17423,8 +19187,12 @@
           <t>Honda</t>
         </is>
       </c>
-      <c r="C1043" t="inlineStr"/>
-      <c r="D1043" t="inlineStr"/>
+      <c r="C1043" t="n">
+        <v>5.210419</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>-74.736192</v>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -17437,8 +19205,12 @@
           <t>Icononzo</t>
         </is>
       </c>
-      <c r="C1044" t="inlineStr"/>
-      <c r="D1044" t="inlineStr"/>
+      <c r="C1044" t="n">
+        <v>4.177615</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>-74.533052</v>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -17451,8 +19223,12 @@
           <t>Lérida</t>
         </is>
       </c>
-      <c r="C1045" t="inlineStr"/>
-      <c r="D1045" t="inlineStr"/>
+      <c r="C1045" t="n">
+        <v>4.860967</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>-74.91094</v>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -17465,8 +19241,12 @@
           <t>Líbano</t>
         </is>
       </c>
-      <c r="C1046" t="inlineStr"/>
-      <c r="D1046" t="inlineStr"/>
+      <c r="C1046" t="n">
+        <v>4.92294</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>-75.064774</v>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
@@ -17479,8 +19259,12 @@
           <t>Sebastián de Mariquita</t>
         </is>
       </c>
-      <c r="C1047" t="inlineStr"/>
-      <c r="D1047" t="inlineStr"/>
+      <c r="C1047" t="n">
+        <v>5.192556</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>-74.886634</v>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
@@ -17493,8 +19277,12 @@
           <t>Melgar</t>
         </is>
       </c>
-      <c r="C1048" t="inlineStr"/>
-      <c r="D1048" t="inlineStr"/>
+      <c r="C1048" t="n">
+        <v>4.203976</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>-74.642948</v>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -17507,8 +19295,12 @@
           <t>Murillo</t>
         </is>
       </c>
-      <c r="C1049" t="inlineStr"/>
-      <c r="D1049" t="inlineStr"/>
+      <c r="C1049" t="n">
+        <v>4.874606</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>-75.171134</v>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -17521,8 +19313,12 @@
           <t>Natagaima</t>
         </is>
       </c>
-      <c r="C1050" t="inlineStr"/>
-      <c r="D1050" t="inlineStr"/>
+      <c r="C1050" t="n">
+        <v>3.624173</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>-75.09306100000001</v>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -17535,8 +19331,12 @@
           <t>Ortega</t>
         </is>
       </c>
-      <c r="C1051" t="inlineStr"/>
-      <c r="D1051" t="inlineStr"/>
+      <c r="C1051" t="n">
+        <v>3.934021</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>-75.221267</v>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
@@ -17549,8 +19349,12 @@
           <t>Palocabildo</t>
         </is>
       </c>
-      <c r="C1052" t="inlineStr"/>
-      <c r="D1052" t="inlineStr"/>
+      <c r="C1052" t="n">
+        <v>5.121992</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>-75.022227</v>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -17563,8 +19367,12 @@
           <t>Piedras</t>
         </is>
       </c>
-      <c r="C1053" t="inlineStr"/>
-      <c r="D1053" t="inlineStr"/>
+      <c r="C1053" t="n">
+        <v>4.542978</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>-74.878879</v>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -17577,8 +19385,12 @@
           <t>Planadas</t>
         </is>
       </c>
-      <c r="C1054" t="inlineStr"/>
-      <c r="D1054" t="inlineStr"/>
+      <c r="C1054" t="n">
+        <v>3.098031</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>-75.856522</v>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -17591,8 +19403,12 @@
           <t>Prado</t>
         </is>
       </c>
-      <c r="C1055" t="inlineStr"/>
-      <c r="D1055" t="inlineStr"/>
+      <c r="C1055" t="n">
+        <v>3.720171</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>-74.862002</v>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
@@ -17605,8 +19421,12 @@
           <t>Purificación</t>
         </is>
       </c>
-      <c r="C1056" t="inlineStr"/>
-      <c r="D1056" t="inlineStr"/>
+      <c r="C1056" t="n">
+        <v>3.858211</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>-74.93082200000001</v>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
@@ -17619,8 +19439,12 @@
           <t>Rioblanco</t>
         </is>
       </c>
-      <c r="C1057" t="inlineStr"/>
-      <c r="D1057" t="inlineStr"/>
+      <c r="C1057" t="n">
+        <v>3.531072</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>-75.64520899999999</v>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
@@ -17633,8 +19457,12 @@
           <t>Roncesvalles</t>
         </is>
       </c>
-      <c r="C1058" t="inlineStr"/>
-      <c r="D1058" t="inlineStr"/>
+      <c r="C1058" t="n">
+        <v>4.011132</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>-75.60519499999999</v>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
@@ -17647,8 +19475,12 @@
           <t>Rovira</t>
         </is>
       </c>
-      <c r="C1059" t="inlineStr"/>
-      <c r="D1059" t="inlineStr"/>
+      <c r="C1059" t="n">
+        <v>4.239339</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>-75.23999999999999</v>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -17661,8 +19493,12 @@
           <t>Saldaña</t>
         </is>
       </c>
-      <c r="C1060" t="inlineStr"/>
-      <c r="D1060" t="inlineStr"/>
+      <c r="C1060" t="n">
+        <v>3.929283</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>-75.01484600000001</v>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
@@ -17675,8 +19511,12 @@
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="C1061" t="inlineStr"/>
-      <c r="D1061" t="inlineStr"/>
+      <c r="C1061" t="n">
+        <v>3.971341</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>-75.514516</v>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
@@ -17689,8 +19529,12 @@
           <t>San Luis</t>
         </is>
       </c>
-      <c r="C1062" t="inlineStr"/>
-      <c r="D1062" t="inlineStr"/>
+      <c r="C1062" t="n">
+        <v>4.134138</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>-75.094696</v>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -17703,8 +19547,12 @@
           <t>Santa Isabel</t>
         </is>
       </c>
-      <c r="C1063" t="inlineStr"/>
-      <c r="D1063" t="inlineStr"/>
+      <c r="C1063" t="n">
+        <v>4.714425</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>-75.098832</v>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -17717,8 +19565,12 @@
           <t>Suárez</t>
         </is>
       </c>
-      <c r="C1064" t="inlineStr"/>
-      <c r="D1064" t="inlineStr"/>
+      <c r="C1064" t="n">
+        <v>4.048489</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>-74.833034</v>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -17731,8 +19583,12 @@
           <t>Valle de San Juan</t>
         </is>
       </c>
-      <c r="C1065" t="inlineStr"/>
-      <c r="D1065" t="inlineStr"/>
+      <c r="C1065" t="n">
+        <v>4.200358</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>-75.11806900000001</v>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -17745,8 +19601,12 @@
           <t>Venadillo</t>
         </is>
       </c>
-      <c r="C1066" t="inlineStr"/>
-      <c r="D1066" t="inlineStr"/>
+      <c r="C1066" t="n">
+        <v>4.719088</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>-74.929669</v>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -17759,8 +19619,12 @@
           <t>Villahermosa</t>
         </is>
       </c>
-      <c r="C1067" t="inlineStr"/>
-      <c r="D1067" t="inlineStr"/>
+      <c r="C1067" t="n">
+        <v>4.976589</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>-75.166612</v>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
@@ -17773,8 +19637,12 @@
           <t>Villarrica</t>
         </is>
       </c>
-      <c r="C1068" t="inlineStr"/>
-      <c r="D1068" t="inlineStr"/>
+      <c r="C1068" t="n">
+        <v>3.935484</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>-74.600269</v>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
@@ -17787,8 +19655,12 @@
           <t>Alcalá</t>
         </is>
       </c>
-      <c r="C1069" t="inlineStr"/>
-      <c r="D1069" t="inlineStr"/>
+      <c r="C1069" t="n">
+        <v>4.674894</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>-75.78166899999999</v>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
@@ -17801,8 +19673,12 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="C1070" t="inlineStr"/>
-      <c r="D1070" t="inlineStr"/>
+      <c r="C1070" t="n">
+        <v>4.16942</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>-76.167062</v>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -17815,8 +19691,12 @@
           <t>Ansermanuevo</t>
         </is>
       </c>
-      <c r="C1071" t="inlineStr"/>
-      <c r="D1071" t="inlineStr"/>
+      <c r="C1071" t="n">
+        <v>4.795705</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>-75.99378299999999</v>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
@@ -17829,8 +19709,12 @@
           <t>Argelia</t>
         </is>
       </c>
-      <c r="C1072" t="inlineStr"/>
-      <c r="D1072" t="inlineStr"/>
+      <c r="C1072" t="n">
+        <v>4.727007</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>-76.121309</v>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
@@ -17843,8 +19727,12 @@
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="C1073" t="inlineStr"/>
-      <c r="D1073" t="inlineStr"/>
+      <c r="C1073" t="n">
+        <v>4.337236</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>-76.18476800000001</v>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
@@ -17857,8 +19745,12 @@
           <t>Buenaventura</t>
         </is>
       </c>
-      <c r="C1074" t="inlineStr"/>
-      <c r="D1074" t="inlineStr"/>
+      <c r="C1074" t="n">
+        <v>3.881671</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>-77.010047</v>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
@@ -17871,8 +19763,12 @@
           <t>Buga</t>
         </is>
       </c>
-      <c r="C1075" t="inlineStr"/>
-      <c r="D1075" t="inlineStr"/>
+      <c r="C1075" t="n">
+        <v>3.900058</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>-76.302013</v>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
@@ -17885,8 +19781,12 @@
           <t>Bugalagrande</t>
         </is>
       </c>
-      <c r="C1076" t="inlineStr"/>
-      <c r="D1076" t="inlineStr"/>
+      <c r="C1076" t="n">
+        <v>4.213888</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>-76.157113</v>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -17899,8 +19799,12 @@
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="C1077" t="inlineStr"/>
-      <c r="D1077" t="inlineStr"/>
+      <c r="C1077" t="n">
+        <v>4.335448</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>-75.826652</v>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -17913,8 +19817,12 @@
           <t>Cali</t>
         </is>
       </c>
-      <c r="C1078" t="inlineStr"/>
-      <c r="D1078" t="inlineStr"/>
+      <c r="C1078" t="n">
+        <v>3.451999</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>-76.532526</v>
+      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -17927,8 +19835,12 @@
           <t>Calima - El Darién</t>
         </is>
       </c>
-      <c r="C1079" t="inlineStr"/>
-      <c r="D1079" t="inlineStr"/>
+      <c r="C1079" t="n">
+        <v>3.931819</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>-76.484241</v>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -17941,8 +19853,12 @@
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="C1080" t="inlineStr"/>
-      <c r="D1080" t="inlineStr"/>
+      <c r="C1080" t="n">
+        <v>3.409048</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>-76.347379</v>
+      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -17955,8 +19871,12 @@
           <t>Cartago</t>
         </is>
       </c>
-      <c r="C1081" t="inlineStr"/>
-      <c r="D1081" t="inlineStr"/>
+      <c r="C1081" t="n">
+        <v>4.710659</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>-75.932388</v>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
@@ -17969,8 +19889,12 @@
           <t>Dagua</t>
         </is>
       </c>
-      <c r="C1082" t="inlineStr"/>
-      <c r="D1082" t="inlineStr"/>
+      <c r="C1082" t="n">
+        <v>3.658161</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>-76.689397</v>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
@@ -17983,8 +19907,12 @@
           <t>El Águila</t>
         </is>
       </c>
-      <c r="C1083" t="inlineStr"/>
-      <c r="D1083" t="inlineStr"/>
+      <c r="C1083" t="n">
+        <v>4.938154</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>-76.060298</v>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
@@ -17997,8 +19925,12 @@
           <t>El Cairo</t>
         </is>
       </c>
-      <c r="C1084" t="inlineStr"/>
-      <c r="D1084" t="inlineStr"/>
+      <c r="C1084" t="n">
+        <v>4.762418</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>-76.220755</v>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
@@ -18011,8 +19943,12 @@
           <t>El Cerrito</t>
         </is>
       </c>
-      <c r="C1085" t="inlineStr"/>
-      <c r="D1085" t="inlineStr"/>
+      <c r="C1085" t="n">
+        <v>3.682918</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>-76.307149</v>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -18025,8 +19961,12 @@
           <t>El Dovio</t>
         </is>
       </c>
-      <c r="C1086" t="inlineStr"/>
-      <c r="D1086" t="inlineStr"/>
+      <c r="C1086" t="n">
+        <v>4.511899</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>-76.238102</v>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
@@ -18039,8 +19979,12 @@
           <t>Florida</t>
         </is>
       </c>
-      <c r="C1087" t="inlineStr"/>
-      <c r="D1087" t="inlineStr"/>
+      <c r="C1087" t="n">
+        <v>3.325601</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>-76.23701199999999</v>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
@@ -18053,8 +19997,12 @@
           <t>Ginebra</t>
         </is>
       </c>
-      <c r="C1088" t="inlineStr"/>
-      <c r="D1088" t="inlineStr"/>
+      <c r="C1088" t="n">
+        <v>3.723705</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>-76.268799</v>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
@@ -18067,8 +20015,12 @@
           <t>Guacarí</t>
         </is>
       </c>
-      <c r="C1089" t="inlineStr"/>
-      <c r="D1089" t="inlineStr"/>
+      <c r="C1089" t="n">
+        <v>3.763024</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>-76.334485</v>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
@@ -18081,8 +20033,12 @@
           <t>Jamundí</t>
         </is>
       </c>
-      <c r="C1090" t="inlineStr"/>
-      <c r="D1090" t="inlineStr"/>
+      <c r="C1090" t="n">
+        <v>3.261046</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>-76.540824</v>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -18095,8 +20051,12 @@
           <t>La Cumbre</t>
         </is>
       </c>
-      <c r="C1091" t="inlineStr"/>
-      <c r="D1091" t="inlineStr"/>
+      <c r="C1091" t="n">
+        <v>3.650589</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>-76.569897</v>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -18109,8 +20069,12 @@
           <t>La Unión</t>
         </is>
       </c>
-      <c r="C1092" t="inlineStr"/>
-      <c r="D1092" t="inlineStr"/>
+      <c r="C1092" t="n">
+        <v>4.537341</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>-76.104472</v>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -18123,8 +20087,12 @@
           <t>La Victoria</t>
         </is>
       </c>
-      <c r="C1093" t="inlineStr"/>
-      <c r="D1093" t="inlineStr"/>
+      <c r="C1093" t="n">
+        <v>4.52325</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>-76.035783</v>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -18137,8 +20105,12 @@
           <t>Obando</t>
         </is>
       </c>
-      <c r="C1094" t="inlineStr"/>
-      <c r="D1094" t="inlineStr"/>
+      <c r="C1094" t="n">
+        <v>4.574658</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>-75.972178</v>
+      </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -18151,8 +20123,12 @@
           <t>Palmira</t>
         </is>
       </c>
-      <c r="C1095" t="inlineStr"/>
-      <c r="D1095" t="inlineStr"/>
+      <c r="C1095" t="n">
+        <v>3.530837</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>-76.298805</v>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -18165,8 +20141,12 @@
           <t>Pradera</t>
         </is>
       </c>
-      <c r="C1096" t="inlineStr"/>
-      <c r="D1096" t="inlineStr"/>
+      <c r="C1096" t="n">
+        <v>3.419669</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>-76.24243800000001</v>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -18179,8 +20159,12 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="C1097" t="inlineStr"/>
-      <c r="D1097" t="inlineStr"/>
+      <c r="C1097" t="n">
+        <v>3.822009</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>-76.522254</v>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
@@ -18193,8 +20177,12 @@
           <t>Riofrío</t>
         </is>
       </c>
-      <c r="C1098" t="inlineStr"/>
-      <c r="D1098" t="inlineStr"/>
+      <c r="C1098" t="n">
+        <v>4.107148</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>-76.383942</v>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -18207,8 +20195,12 @@
           <t>Roldanillo</t>
         </is>
       </c>
-      <c r="C1099" t="inlineStr"/>
-      <c r="D1099" t="inlineStr"/>
+      <c r="C1099" t="n">
+        <v>4.409117</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>-76.154374</v>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -18221,8 +20213,12 @@
           <t>San Pedro</t>
         </is>
       </c>
-      <c r="C1100" t="inlineStr"/>
-      <c r="D1100" t="inlineStr"/>
+      <c r="C1100" t="n">
+        <v>3.995568</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>-76.228049</v>
+      </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -18235,8 +20231,12 @@
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="C1101" t="inlineStr"/>
-      <c r="D1101" t="inlineStr"/>
+      <c r="C1101" t="n">
+        <v>4.264507</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>-75.93439600000001</v>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -18249,8 +20249,12 @@
           <t>Toro</t>
         </is>
       </c>
-      <c r="C1102" t="inlineStr"/>
-      <c r="D1102" t="inlineStr"/>
+      <c r="C1102" t="n">
+        <v>4.608925</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>-76.082404</v>
+      </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
@@ -18263,8 +20267,12 @@
           <t>Trujillo</t>
         </is>
       </c>
-      <c r="C1103" t="inlineStr"/>
-      <c r="D1103" t="inlineStr"/>
+      <c r="C1103" t="n">
+        <v>4.212304</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>-76.318893</v>
+      </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -18277,8 +20285,12 @@
           <t>Tuluá</t>
         </is>
       </c>
-      <c r="C1104" t="inlineStr"/>
-      <c r="D1104" t="inlineStr"/>
+      <c r="C1104" t="n">
+        <v>4.085667</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>-76.197278</v>
+      </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
@@ -18291,8 +20303,12 @@
           <t>Ulloa</t>
         </is>
       </c>
-      <c r="C1105" t="inlineStr"/>
-      <c r="D1105" t="inlineStr"/>
+      <c r="C1105" t="n">
+        <v>4.708103</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>-75.781254</v>
+      </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
@@ -18305,8 +20321,12 @@
           <t>Versalles</t>
         </is>
       </c>
-      <c r="C1106" t="inlineStr"/>
-      <c r="D1106" t="inlineStr"/>
+      <c r="C1106" t="n">
+        <v>4.574794</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>-76.199704</v>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
@@ -18319,8 +20339,12 @@
           <t>Vijes</t>
         </is>
       </c>
-      <c r="C1107" t="inlineStr"/>
-      <c r="D1107" t="inlineStr"/>
+      <c r="C1107" t="n">
+        <v>3.7004</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>-76.442888</v>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
@@ -18333,8 +20357,12 @@
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="C1108" t="inlineStr"/>
-      <c r="D1108" t="inlineStr"/>
+      <c r="C1108" t="n">
+        <v>3.897661</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>-76.387873</v>
+      </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
@@ -18347,8 +20375,12 @@
           <t>Yumbo</t>
         </is>
       </c>
-      <c r="C1109" t="inlineStr"/>
-      <c r="D1109" t="inlineStr"/>
+      <c r="C1109" t="n">
+        <v>3.583466</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>-76.495222</v>
+      </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
@@ -18361,8 +20393,12 @@
           <t>Zarzal</t>
         </is>
       </c>
-      <c r="C1110" t="inlineStr"/>
-      <c r="D1110" t="inlineStr"/>
+      <c r="C1110" t="n">
+        <v>4.393943</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>-76.07064699999999</v>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
@@ -18375,8 +20411,12 @@
           <t>Carurú</t>
         </is>
       </c>
-      <c r="C1111" t="inlineStr"/>
-      <c r="D1111" t="inlineStr"/>
+      <c r="C1111" t="n">
+        <v>1.015525</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>-71.296148</v>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
@@ -18389,8 +20429,12 @@
           <t>Pacoa</t>
         </is>
       </c>
-      <c r="C1112" t="inlineStr"/>
-      <c r="D1112" t="inlineStr"/>
+      <c r="C1112" t="n">
+        <v>0.194202</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>-70.90745800000001</v>
+      </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
@@ -18403,8 +20447,12 @@
           <t>Papunahua</t>
         </is>
       </c>
-      <c r="C1113" t="inlineStr"/>
-      <c r="D1113" t="inlineStr"/>
+      <c r="C1113" t="n">
+        <v>1.616881</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>-70.928084</v>
+      </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
@@ -18417,8 +20465,12 @@
           <t>Taraira</t>
         </is>
       </c>
-      <c r="C1114" t="inlineStr"/>
-      <c r="D1114" t="inlineStr"/>
+      <c r="C1114" t="n">
+        <v>-0.563016</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>-69.634058</v>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
@@ -18431,8 +20483,12 @@
           <t>Yavaraté</t>
         </is>
       </c>
-      <c r="C1115" t="inlineStr"/>
-      <c r="D1115" t="inlineStr"/>
+      <c r="C1115" t="n">
+        <v>0.831421</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>-69.634244</v>
+      </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
@@ -18445,8 +20501,12 @@
           <t>Mitú</t>
         </is>
       </c>
-      <c r="C1116" t="inlineStr"/>
-      <c r="D1116" t="inlineStr"/>
+      <c r="C1116" t="n">
+        <v>1.258018</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>-70.123733</v>
+      </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
@@ -18459,8 +20519,12 @@
           <t>Cumaribo</t>
         </is>
       </c>
-      <c r="C1117" t="inlineStr"/>
-      <c r="D1117" t="inlineStr"/>
+      <c r="C1117" t="n">
+        <v>4.44715</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>-69.797584</v>
+      </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
@@ -18473,8 +20537,12 @@
           <t>La Primavera</t>
         </is>
       </c>
-      <c r="C1118" t="inlineStr"/>
-      <c r="D1118" t="inlineStr"/>
+      <c r="C1118" t="n">
+        <v>5.490457</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>-70.409767</v>
+      </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
@@ -18487,8 +20555,12 @@
           <t>Santa Rosalía</t>
         </is>
       </c>
-      <c r="C1119" t="inlineStr"/>
-      <c r="D1119" t="inlineStr"/>
+      <c r="C1119" t="n">
+        <v>5.141291</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>-70.85740300000001</v>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
@@ -18501,8 +20573,12 @@
           <t>Puerto Carreño</t>
         </is>
       </c>
-      <c r="C1120" t="inlineStr"/>
-      <c r="D1120" t="inlineStr"/>
+      <c r="C1120" t="n">
+        <v>6.190923</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>-67.484189</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
